--- a/research/traditional_assets/database/data/peru/peru_precious_metals.xlsx
+++ b/research/traditional_assets/database/data/peru/peru_precious_metals.xlsx
@@ -1406,7 +1406,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1543,22 +1543,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1127191100881549</v>
+        <v>0.1124183137133948</v>
       </c>
       <c r="C2">
-        <v>1727.306449038785</v>
+        <v>1717.579679923921</v>
       </c>
       <c r="D2">
-        <v>1695.206449038785</v>
+        <v>1702.860679923921</v>
       </c>
       <c r="E2">
-        <v>-41.2</v>
+        <v>-23.819</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>17.381</v>
       </c>
       <c r="G2">
         <v>32.1</v>
@@ -1579,28 +1579,28 @@
         <v>161.6</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.8742643</v>
       </c>
       <c r="N2">
-        <v>161.6</v>
+        <v>160.7257357</v>
       </c>
       <c r="O2">
-        <v>47.672</v>
+        <v>47.4140920315</v>
       </c>
       <c r="P2">
-        <v>113.928</v>
+        <v>113.3116436685</v>
       </c>
       <c r="Q2">
-        <v>206.128</v>
+        <v>205.5116436685</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1127191100881549</v>
+        <v>0.1131956552660554</v>
       </c>
       <c r="T2">
-        <v>1.035217350236429</v>
+        <v>1.042589352579022</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1617,7 +1617,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>184.8411287067309</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1625,22 +1625,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1124183137133948</v>
+        <v>0.1121175173386347</v>
       </c>
       <c r="C3">
-        <v>1717.579679923921</v>
+        <v>1707.922345401732</v>
       </c>
       <c r="D3">
-        <v>1702.860679923921</v>
+        <v>1710.584345401732</v>
       </c>
       <c r="E3">
-        <v>-23.819</v>
+        <v>-6.438000000000002</v>
       </c>
       <c r="F3">
-        <v>17.381</v>
+        <v>34.762</v>
       </c>
       <c r="G3">
         <v>32.1</v>
@@ -1661,28 +1661,28 @@
         <v>161.6</v>
       </c>
       <c r="M3">
-        <v>0.8742643</v>
+        <v>1.7485286</v>
       </c>
       <c r="N3">
-        <v>160.7257357</v>
+        <v>159.8514714</v>
       </c>
       <c r="O3">
-        <v>47.4140920315</v>
+        <v>47.156184063</v>
       </c>
       <c r="P3">
-        <v>113.3116436685</v>
+        <v>112.695287337</v>
       </c>
       <c r="Q3">
-        <v>205.5116436685</v>
+        <v>204.895287337</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1131956552660554</v>
+        <v>0.1136819258557497</v>
       </c>
       <c r="T3">
-        <v>1.042589352579022</v>
+        <v>1.050111803949014</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>184.8411287067309</v>
+        <v>92.42056435336546</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1707,22 +1707,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1121175173386347</v>
+        <v>0.1118167209638747</v>
       </c>
       <c r="C4">
-        <v>1707.922345401732</v>
+        <v>1698.335394580572</v>
       </c>
       <c r="D4">
-        <v>1710.584345401732</v>
+        <v>1718.378394580573</v>
       </c>
       <c r="E4">
-        <v>-6.438000000000002</v>
+        <v>10.943</v>
       </c>
       <c r="F4">
-        <v>34.762</v>
+        <v>52.143</v>
       </c>
       <c r="G4">
         <v>32.1</v>
@@ -1743,28 +1743,28 @@
         <v>161.6</v>
       </c>
       <c r="M4">
-        <v>1.7485286</v>
+        <v>2.6227929</v>
       </c>
       <c r="N4">
-        <v>159.8514714</v>
+        <v>158.9772071</v>
       </c>
       <c r="O4">
-        <v>47.156184063</v>
+        <v>46.89827609449999</v>
       </c>
       <c r="P4">
-        <v>112.695287337</v>
+        <v>112.0789310055</v>
       </c>
       <c r="Q4">
-        <v>204.895287337</v>
+        <v>204.2789310055</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1136819258557497</v>
+        <v>0.1141782226431698</v>
       </c>
       <c r="T4">
-        <v>1.050111803949014</v>
+        <v>1.05778935740911</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1781,7 +1781,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>92.42056435336546</v>
+        <v>61.6137095689103</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1789,22 +1789,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1118167209638747</v>
+        <v>0.1115159245891146</v>
       </c>
       <c r="C5">
-        <v>1698.335394580572</v>
+        <v>1688.81979394591</v>
       </c>
       <c r="D5">
-        <v>1718.378394580573</v>
+        <v>1726.24379394591</v>
       </c>
       <c r="E5">
-        <v>10.943</v>
+        <v>28.324</v>
       </c>
       <c r="F5">
-        <v>52.143</v>
+        <v>69.524</v>
       </c>
       <c r="G5">
         <v>32.1</v>
@@ -1825,28 +1825,28 @@
         <v>161.6</v>
       </c>
       <c r="M5">
-        <v>2.6227929</v>
+        <v>3.4970572</v>
       </c>
       <c r="N5">
-        <v>158.9772071</v>
+        <v>158.1029428</v>
       </c>
       <c r="O5">
-        <v>46.89827609449999</v>
+        <v>46.640368126</v>
       </c>
       <c r="P5">
-        <v>112.0789310055</v>
+        <v>111.462574674</v>
       </c>
       <c r="Q5">
-        <v>204.2789310055</v>
+        <v>203.662574674</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1141782226431698</v>
+        <v>0.1146848589469944</v>
       </c>
       <c r="T5">
-        <v>1.05778935740911</v>
+        <v>1.065626859899624</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1863,7 +1863,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>61.6137095689103</v>
+        <v>46.21028217668272</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1871,22 +1871,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1115159245891146</v>
+        <v>0.1112151282143546</v>
       </c>
       <c r="C6">
-        <v>1688.81979394591</v>
+        <v>1679.37652775986</v>
       </c>
       <c r="D6">
-        <v>1726.24379394591</v>
+        <v>1734.181527759861</v>
       </c>
       <c r="E6">
-        <v>28.324</v>
+        <v>45.70500000000001</v>
       </c>
       <c r="F6">
-        <v>69.524</v>
+        <v>86.90500000000002</v>
       </c>
       <c r="G6">
         <v>32.1</v>
@@ -1907,28 +1907,28 @@
         <v>161.6</v>
       </c>
       <c r="M6">
-        <v>3.4970572</v>
+        <v>4.371321500000001</v>
       </c>
       <c r="N6">
-        <v>158.1029428</v>
+        <v>157.2286785</v>
       </c>
       <c r="O6">
-        <v>46.640368126</v>
+        <v>46.3824601575</v>
       </c>
       <c r="P6">
-        <v>111.462574674</v>
+        <v>110.8462183425</v>
       </c>
       <c r="Q6">
-        <v>203.662574674</v>
+        <v>203.0462183425</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1146848589469944</v>
+        <v>0.115202161278268</v>
       </c>
       <c r="T6">
-        <v>1.065626859899624</v>
+        <v>1.07362936244257</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1945,7 +1945,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>46.21028217668272</v>
+        <v>36.96822574134617</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1953,22 +1953,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1112151282143546</v>
+        <v>0.1109143318395945</v>
       </c>
       <c r="C7">
-        <v>1679.37652775986</v>
+        <v>1670.006598471775</v>
       </c>
       <c r="D7">
-        <v>1734.181527759861</v>
+        <v>1742.192598471775</v>
       </c>
       <c r="E7">
-        <v>45.70500000000001</v>
+        <v>63.08600000000001</v>
       </c>
       <c r="F7">
-        <v>86.90500000000002</v>
+        <v>104.286</v>
       </c>
       <c r="G7">
         <v>32.1</v>
@@ -1989,28 +1989,28 @@
         <v>161.6</v>
       </c>
       <c r="M7">
-        <v>4.371321500000001</v>
+        <v>5.245585800000001</v>
       </c>
       <c r="N7">
-        <v>157.2286785</v>
+        <v>156.3544142</v>
       </c>
       <c r="O7">
-        <v>46.3824601575</v>
+        <v>46.124552189</v>
       </c>
       <c r="P7">
-        <v>110.8462183425</v>
+        <v>110.229862011</v>
       </c>
       <c r="Q7">
-        <v>203.0462183425</v>
+        <v>202.429862011</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.115202161278268</v>
+        <v>0.1157304700421218</v>
       </c>
       <c r="T7">
-        <v>1.07362936244257</v>
+        <v>1.081802130997068</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>36.96822574134617</v>
+        <v>30.80685478445515</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2035,22 +2035,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1109143318395945</v>
+        <v>0.1106135354648345</v>
       </c>
       <c r="C8">
-        <v>1670.006598471775</v>
+        <v>1660.711027140273</v>
       </c>
       <c r="D8">
-        <v>1742.192598471775</v>
+        <v>1750.278027140273</v>
       </c>
       <c r="E8">
-        <v>63.086</v>
+        <v>80.467</v>
       </c>
       <c r="F8">
-        <v>104.286</v>
+        <v>121.667</v>
       </c>
       <c r="G8">
         <v>32.1</v>
@@ -2071,28 +2071,28 @@
         <v>161.6</v>
       </c>
       <c r="M8">
-        <v>5.2455858</v>
+        <v>6.1198501</v>
       </c>
       <c r="N8">
-        <v>156.3544142</v>
+        <v>155.4801499</v>
       </c>
       <c r="O8">
-        <v>46.124552189</v>
+        <v>45.86664422049999</v>
       </c>
       <c r="P8">
-        <v>110.229862011</v>
+        <v>109.6135056795</v>
       </c>
       <c r="Q8">
-        <v>202.429862011</v>
+        <v>201.8135056795</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1157304700421218</v>
+        <v>0.1162701402847682</v>
       </c>
       <c r="T8">
-        <v>1.081802130997068</v>
+        <v>1.090150658015104</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2109,7 +2109,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>30.80685478445515</v>
+        <v>26.40587552953298</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2117,22 +2117,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1106135354648344</v>
+        <v>0.1103127390900744</v>
       </c>
       <c r="C9">
-        <v>1660.711027140273</v>
+        <v>1651.490853867083</v>
       </c>
       <c r="D9">
-        <v>1750.278027140273</v>
+        <v>1758.438853867083</v>
       </c>
       <c r="E9">
-        <v>80.46700000000001</v>
+        <v>97.848</v>
       </c>
       <c r="F9">
-        <v>121.667</v>
+        <v>139.048</v>
       </c>
       <c r="G9">
         <v>32.1</v>
@@ -2153,28 +2153,28 @@
         <v>161.6</v>
       </c>
       <c r="M9">
-        <v>6.119850100000001</v>
+        <v>6.9941144</v>
       </c>
       <c r="N9">
-        <v>155.4801499</v>
+        <v>154.6058856</v>
       </c>
       <c r="O9">
-        <v>45.86664422049999</v>
+        <v>45.60873625199999</v>
       </c>
       <c r="P9">
-        <v>109.6135056795</v>
+        <v>108.997149348</v>
       </c>
       <c r="Q9">
-        <v>201.8135056795</v>
+        <v>201.197149348</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1162701402847682</v>
+        <v>0.1168215424892113</v>
       </c>
       <c r="T9">
-        <v>1.090150658015104</v>
+        <v>1.098680674750923</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2191,7 +2191,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>26.40587552953298</v>
+        <v>23.10514108834136</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2199,22 +2199,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1103127390900744</v>
+        <v>0.1100119427153144</v>
       </c>
       <c r="C10">
-        <v>1651.490853867083</v>
+        <v>1642.347138243066</v>
       </c>
       <c r="D10">
-        <v>1758.438853867083</v>
+        <v>1766.676138243067</v>
       </c>
       <c r="E10">
-        <v>97.848</v>
+        <v>115.229</v>
       </c>
       <c r="F10">
-        <v>139.048</v>
+        <v>156.429</v>
       </c>
       <c r="G10">
         <v>32.1</v>
@@ -2235,28 +2235,28 @@
         <v>161.6</v>
       </c>
       <c r="M10">
-        <v>6.9941144</v>
+        <v>7.8683787</v>
       </c>
       <c r="N10">
-        <v>154.6058856</v>
+        <v>153.7316213</v>
       </c>
       <c r="O10">
-        <v>45.60873625199999</v>
+        <v>45.3508282835</v>
       </c>
       <c r="P10">
-        <v>108.997149348</v>
+        <v>108.3807930165</v>
       </c>
       <c r="Q10">
-        <v>201.197149348</v>
+        <v>200.5807930165</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1168215424892113</v>
+        <v>0.1173850634234224</v>
       </c>
       <c r="T10">
-        <v>1.098680674750923</v>
+        <v>1.107398164382035</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2273,7 +2273,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>23.10514108834136</v>
+        <v>20.53790318963677</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2281,22 +2281,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1100119427153144</v>
+        <v>0.1097111463405543</v>
       </c>
       <c r="C11">
-        <v>1642.347138243066</v>
+        <v>1633.280959806851</v>
       </c>
       <c r="D11">
-        <v>1766.676138243067</v>
+        <v>1774.990959806851</v>
       </c>
       <c r="E11">
-        <v>115.229</v>
+        <v>132.61</v>
       </c>
       <c r="F11">
-        <v>156.429</v>
+        <v>173.81</v>
       </c>
       <c r="G11">
         <v>32.1</v>
@@ -2317,28 +2317,28 @@
         <v>161.6</v>
       </c>
       <c r="M11">
-        <v>7.8683787</v>
+        <v>8.742642999999999</v>
       </c>
       <c r="N11">
-        <v>153.7316213</v>
+        <v>152.857357</v>
       </c>
       <c r="O11">
-        <v>45.3508282835</v>
+        <v>45.092920315</v>
       </c>
       <c r="P11">
-        <v>108.3807930165</v>
+        <v>107.764436685</v>
       </c>
       <c r="Q11">
-        <v>200.5807930165</v>
+        <v>199.964436685</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1173850634234224</v>
+        <v>0.1179611070450603</v>
       </c>
       <c r="T11">
-        <v>1.107398164382035</v>
+        <v>1.116309376004949</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>20.53790318963677</v>
+        <v>18.48411287067309</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2363,22 +2363,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1097111463405543</v>
+        <v>0.1094103499657942</v>
       </c>
       <c r="C12">
-        <v>1633.280959806851</v>
+        <v>1624.293418516462</v>
       </c>
       <c r="D12">
-        <v>1774.990959806851</v>
+        <v>1783.384418516462</v>
       </c>
       <c r="E12">
-        <v>132.61</v>
+        <v>149.991</v>
       </c>
       <c r="F12">
-        <v>173.81</v>
+        <v>191.191</v>
       </c>
       <c r="G12">
         <v>32.1</v>
@@ -2399,28 +2399,28 @@
         <v>161.6</v>
       </c>
       <c r="M12">
-        <v>8.742643000000001</v>
+        <v>9.616907299999999</v>
       </c>
       <c r="N12">
-        <v>152.857357</v>
+        <v>151.9830927</v>
       </c>
       <c r="O12">
-        <v>45.09292031499999</v>
+        <v>44.83501234649999</v>
       </c>
       <c r="P12">
-        <v>107.764436685</v>
+        <v>107.1480803535</v>
       </c>
       <c r="Q12">
-        <v>199.964436685</v>
+        <v>199.3480803535</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1179611070450603</v>
+        <v>0.1185500954671845</v>
       </c>
       <c r="T12">
-        <v>1.116309376004949</v>
+        <v>1.125420839574446</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>18.48411287067309</v>
+        <v>16.80373897333917</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1094103499657942</v>
+        <v>0.1091095535910342</v>
       </c>
       <c r="C13">
-        <v>1624.293418516462</v>
+        <v>1615.385635234408</v>
       </c>
       <c r="D13">
-        <v>1783.384418516462</v>
+        <v>1791.857635234408</v>
       </c>
       <c r="E13">
-        <v>149.991</v>
+        <v>167.372</v>
       </c>
       <c r="F13">
-        <v>191.191</v>
+        <v>208.572</v>
       </c>
       <c r="G13">
         <v>32.1</v>
@@ -2481,28 +2481,28 @@
         <v>161.6</v>
       </c>
       <c r="M13">
-        <v>9.616907299999999</v>
+        <v>10.4911716</v>
       </c>
       <c r="N13">
-        <v>151.9830927</v>
+        <v>151.1088284</v>
       </c>
       <c r="O13">
-        <v>44.83501234649999</v>
+        <v>44.57710437799999</v>
       </c>
       <c r="P13">
-        <v>107.1480803535</v>
+        <v>106.531724022</v>
       </c>
       <c r="Q13">
-        <v>199.3480803535</v>
+        <v>198.731724022</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1185500954671845</v>
+        <v>0.1191524699898116</v>
       </c>
       <c r="T13">
-        <v>1.125420839574446</v>
+        <v>1.134739381861431</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2519,7 +2519,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>16.80373897333917</v>
+        <v>15.40342739222758</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2527,22 +2527,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1091095535910342</v>
+        <v>0.1088087572162741</v>
       </c>
       <c r="C14">
-        <v>1615.385635234408</v>
+        <v>1606.558752226664</v>
       </c>
       <c r="D14">
-        <v>1791.857635234408</v>
+        <v>1800.411752226664</v>
       </c>
       <c r="E14">
-        <v>167.372</v>
+        <v>184.753</v>
       </c>
       <c r="F14">
-        <v>208.572</v>
+        <v>225.953</v>
       </c>
       <c r="G14">
         <v>32.1</v>
@@ -2563,28 +2563,28 @@
         <v>161.6</v>
       </c>
       <c r="M14">
-        <v>10.4911716</v>
+        <v>11.3654359</v>
       </c>
       <c r="N14">
-        <v>151.1088284</v>
+        <v>150.2345641</v>
       </c>
       <c r="O14">
-        <v>44.57710437799999</v>
+        <v>44.31919640949999</v>
       </c>
       <c r="P14">
-        <v>106.531724022</v>
+        <v>105.9153676905</v>
       </c>
       <c r="Q14">
-        <v>198.731724022</v>
+        <v>198.1153676905</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1191524699898116</v>
+        <v>0.1197686922026139</v>
       </c>
       <c r="T14">
-        <v>1.134739381861431</v>
+        <v>1.144272143511336</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2601,7 +2601,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>15.40342739222758</v>
+        <v>14.21854836205622</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2609,22 +2609,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1088087572162741</v>
+        <v>0.108507960841514</v>
       </c>
       <c r="C15">
-        <v>1606.558752226664</v>
+        <v>1597.813933676001</v>
       </c>
       <c r="D15">
-        <v>1800.411752226664</v>
+        <v>1809.047933676001</v>
       </c>
       <c r="E15">
-        <v>184.753</v>
+        <v>202.134</v>
       </c>
       <c r="F15">
-        <v>225.953</v>
+        <v>243.334</v>
       </c>
       <c r="G15">
         <v>32.1</v>
@@ -2645,28 +2645,28 @@
         <v>161.6</v>
       </c>
       <c r="M15">
-        <v>11.3654359</v>
+        <v>12.2397002</v>
       </c>
       <c r="N15">
-        <v>150.2345641</v>
+        <v>149.3602998</v>
       </c>
       <c r="O15">
-        <v>44.31919640949999</v>
+        <v>44.061288441</v>
       </c>
       <c r="P15">
-        <v>105.9153676905</v>
+        <v>105.299011359</v>
       </c>
       <c r="Q15">
-        <v>198.1153676905</v>
+        <v>197.499011359</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1197686922026139</v>
+        <v>0.1203992451645512</v>
       </c>
       <c r="T15">
-        <v>1.144272143511336</v>
+        <v>1.154026597292633</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>14.21854836205622</v>
+        <v>13.20293776476649</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2691,22 +2691,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.108507960841514</v>
+        <v>0.108365789466754</v>
       </c>
       <c r="C16">
-        <v>1597.813933676001</v>
+        <v>1584.543723836719</v>
       </c>
       <c r="D16">
-        <v>1809.047933676001</v>
+        <v>1813.158723836719</v>
       </c>
       <c r="E16">
-        <v>202.134</v>
+        <v>219.515</v>
       </c>
       <c r="F16">
-        <v>243.334</v>
+        <v>260.715</v>
       </c>
       <c r="G16">
         <v>32.1</v>
@@ -2727,45 +2727,45 @@
         <v>161.6</v>
       </c>
       <c r="M16">
-        <v>12.2397002</v>
+        <v>13.505037</v>
       </c>
       <c r="N16">
-        <v>149.3602998</v>
+        <v>148.094963</v>
       </c>
       <c r="O16">
-        <v>44.061288441</v>
+        <v>43.688014085</v>
       </c>
       <c r="P16">
-        <v>105.299011359</v>
+        <v>104.406948915</v>
       </c>
       <c r="Q16">
-        <v>197.499011359</v>
+        <v>196.606948915</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1203992451645512</v>
+        <v>0.1210446346667694</v>
       </c>
       <c r="T16">
-        <v>1.154026597292633</v>
+        <v>1.164010567633491</v>
       </c>
       <c r="U16">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V16">
         <v>0.295</v>
       </c>
       <c r="W16">
-        <v>0.0354615</v>
+        <v>0.036519</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y16">
-        <v>13.20293776476649</v>
+        <v>11.96590575797756</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2773,22 +2773,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.108365789466754</v>
+        <v>0.1080755680919939</v>
       </c>
       <c r="C17">
-        <v>1584.543723836719</v>
+        <v>1575.612545068584</v>
       </c>
       <c r="D17">
-        <v>1813.158723836719</v>
+        <v>1821.608545068584</v>
       </c>
       <c r="E17">
-        <v>219.515</v>
+        <v>236.896</v>
       </c>
       <c r="F17">
-        <v>260.715</v>
+        <v>278.096</v>
       </c>
       <c r="G17">
         <v>32.1</v>
@@ -2809,28 +2809,28 @@
         <v>161.6</v>
       </c>
       <c r="M17">
-        <v>13.505037</v>
+        <v>14.4053728</v>
       </c>
       <c r="N17">
-        <v>148.094963</v>
+        <v>147.1946272</v>
       </c>
       <c r="O17">
-        <v>43.688014085</v>
+        <v>43.422415024</v>
       </c>
       <c r="P17">
-        <v>104.406948915</v>
+        <v>103.772212176</v>
       </c>
       <c r="Q17">
-        <v>196.606948915</v>
+        <v>195.972212176</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1210446346667694</v>
+        <v>0.1217053905857071</v>
       </c>
       <c r="T17">
-        <v>1.164010567633491</v>
+        <v>1.174232251553892</v>
       </c>
       <c r="U17">
         <v>0.0518</v>
@@ -2847,7 +2847,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>11.96590575797756</v>
+        <v>11.21803664810396</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2855,22 +2855,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1080755680919939</v>
+        <v>0.1077853467172339</v>
       </c>
       <c r="C18">
-        <v>1575.612545068584</v>
+        <v>1566.760492057235</v>
       </c>
       <c r="D18">
-        <v>1821.608545068584</v>
+        <v>1830.137492057235</v>
       </c>
       <c r="E18">
-        <v>236.896</v>
+        <v>254.277</v>
       </c>
       <c r="F18">
-        <v>278.096</v>
+        <v>295.477</v>
       </c>
       <c r="G18">
         <v>32.1</v>
@@ -2891,28 +2891,28 @@
         <v>161.6</v>
       </c>
       <c r="M18">
-        <v>14.4053728</v>
+        <v>15.3057086</v>
       </c>
       <c r="N18">
-        <v>147.1946272</v>
+        <v>146.2942914</v>
       </c>
       <c r="O18">
-        <v>43.422415024</v>
+        <v>43.15681596299999</v>
       </c>
       <c r="P18">
-        <v>103.772212176</v>
+        <v>103.137475437</v>
       </c>
       <c r="Q18">
-        <v>195.972212176</v>
+        <v>195.337475437</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1217053905857071</v>
+        <v>0.1223820683340167</v>
       </c>
       <c r="T18">
-        <v>1.174232251553892</v>
+        <v>1.18470024111093</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2929,7 +2929,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>11.21803664810396</v>
+        <v>10.55815213939196</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2937,22 +2937,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1077853467172339</v>
+        <v>0.1074951253424738</v>
       </c>
       <c r="C19">
-        <v>1566.760492057235</v>
+        <v>1557.988681454231</v>
       </c>
       <c r="D19">
-        <v>1830.137492057235</v>
+        <v>1838.746681454231</v>
       </c>
       <c r="E19">
-        <v>254.277</v>
+        <v>271.6580000000001</v>
       </c>
       <c r="F19">
-        <v>295.477</v>
+        <v>312.8580000000001</v>
       </c>
       <c r="G19">
         <v>32.1</v>
@@ -2973,28 +2973,28 @@
         <v>161.6</v>
       </c>
       <c r="M19">
-        <v>15.3057086</v>
+        <v>16.2060444</v>
       </c>
       <c r="N19">
-        <v>146.2942914</v>
+        <v>145.3939556</v>
       </c>
       <c r="O19">
-        <v>43.15681596299999</v>
+        <v>42.891216902</v>
       </c>
       <c r="P19">
-        <v>103.137475437</v>
+        <v>102.502738698</v>
       </c>
       <c r="Q19">
-        <v>195.337475437</v>
+        <v>194.702738698</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1223820683340167</v>
+        <v>0.123075250417651</v>
       </c>
       <c r="T19">
-        <v>1.18470024111093</v>
+        <v>1.195423547486433</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -3011,7 +3011,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>10.55815213939196</v>
+        <v>9.971588131647966</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3019,22 +3019,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1074951253424738</v>
+        <v>0.1074326189677138</v>
       </c>
       <c r="C20">
-        <v>1557.988681454231</v>
+        <v>1542.47249575362</v>
       </c>
       <c r="D20">
-        <v>1838.746681454231</v>
+        <v>1840.61149575362</v>
       </c>
       <c r="E20">
-        <v>271.658</v>
+        <v>289.039</v>
       </c>
       <c r="F20">
-        <v>312.858</v>
+        <v>330.239</v>
       </c>
       <c r="G20">
         <v>32.1</v>
@@ -3055,45 +3055,45 @@
         <v>161.6</v>
       </c>
       <c r="M20">
-        <v>16.2060444</v>
+        <v>17.6677865</v>
       </c>
       <c r="N20">
-        <v>145.3939556</v>
+        <v>143.9322135</v>
       </c>
       <c r="O20">
-        <v>42.891216902</v>
+        <v>42.46000298249999</v>
       </c>
       <c r="P20">
-        <v>102.502738698</v>
+        <v>101.4722105175</v>
       </c>
       <c r="Q20">
-        <v>194.702738698</v>
+        <v>193.6722105175</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.123075250417651</v>
+        <v>0.1237855481082886</v>
       </c>
       <c r="T20">
-        <v>1.195423547486433</v>
+        <v>1.206411626858861</v>
       </c>
       <c r="U20">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V20">
         <v>0.295</v>
       </c>
       <c r="W20">
-        <v>0.036519</v>
+        <v>0.0377175</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y20">
-        <v>9.971588131647968</v>
+        <v>9.146590038316344</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3101,22 +3101,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1074326189677138</v>
+        <v>0.1071543825929537</v>
       </c>
       <c r="C21">
-        <v>1542.47249575362</v>
+        <v>1533.438496379765</v>
       </c>
       <c r="D21">
-        <v>1840.61149575362</v>
+        <v>1848.958496379765</v>
       </c>
       <c r="E21">
-        <v>289.039</v>
+        <v>306.4200000000001</v>
       </c>
       <c r="F21">
-        <v>330.239</v>
+        <v>347.6200000000001</v>
       </c>
       <c r="G21">
         <v>32.1</v>
@@ -3137,28 +3137,28 @@
         <v>161.6</v>
       </c>
       <c r="M21">
-        <v>17.6677865</v>
+        <v>18.59767</v>
       </c>
       <c r="N21">
-        <v>143.9322135</v>
+        <v>143.00233</v>
       </c>
       <c r="O21">
-        <v>42.46000298249999</v>
+        <v>42.18568734999999</v>
       </c>
       <c r="P21">
-        <v>101.4722105175</v>
+        <v>100.81664265</v>
       </c>
       <c r="Q21">
-        <v>193.6722105175</v>
+        <v>193.01664265</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1237855481082886</v>
+        <v>0.1245136032411922</v>
       </c>
       <c r="T21">
-        <v>1.206411626858861</v>
+        <v>1.2176744082156</v>
       </c>
       <c r="U21">
         <v>0.0535</v>
@@ -3175,7 +3175,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>9.146590038316344</v>
+        <v>8.689260536400525</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3183,22 +3183,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1071543825929537</v>
+        <v>0.1068761462181937</v>
       </c>
       <c r="C22">
-        <v>1533.438496379765</v>
+        <v>1524.480547619388</v>
       </c>
       <c r="D22">
-        <v>1848.958496379765</v>
+        <v>1857.381547619388</v>
       </c>
       <c r="E22">
-        <v>306.4200000000001</v>
+        <v>323.8010000000001</v>
       </c>
       <c r="F22">
-        <v>347.6200000000001</v>
+        <v>365.0010000000001</v>
       </c>
       <c r="G22">
         <v>32.1</v>
@@ -3219,28 +3219,28 @@
         <v>161.6</v>
       </c>
       <c r="M22">
-        <v>18.59767</v>
+        <v>19.5275535</v>
       </c>
       <c r="N22">
-        <v>143.00233</v>
+        <v>142.0724465</v>
       </c>
       <c r="O22">
-        <v>42.18568734999999</v>
+        <v>41.9113717175</v>
       </c>
       <c r="P22">
-        <v>100.81664265</v>
+        <v>100.1610747825</v>
       </c>
       <c r="Q22">
-        <v>193.01664265</v>
+        <v>192.3610747825</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1245136032411922</v>
+        <v>0.1252600901496122</v>
       </c>
       <c r="T22">
-        <v>1.2176744082156</v>
+        <v>1.229222323277573</v>
       </c>
       <c r="U22">
         <v>0.0535</v>
@@ -3257,7 +3257,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>8.689260536400525</v>
+        <v>8.275486225143357</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3265,22 +3265,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1068761462181937</v>
+        <v>0.1065979098434336</v>
       </c>
       <c r="C23">
-        <v>1524.480547619388</v>
+        <v>1515.599693589647</v>
       </c>
       <c r="D23">
-        <v>1857.381547619388</v>
+        <v>1865.881693589647</v>
       </c>
       <c r="E23">
-        <v>323.801</v>
+        <v>341.182</v>
       </c>
       <c r="F23">
-        <v>365.001</v>
+        <v>382.382</v>
       </c>
       <c r="G23">
         <v>32.1</v>
@@ -3301,28 +3301,28 @@
         <v>161.6</v>
       </c>
       <c r="M23">
-        <v>19.5275535</v>
+        <v>20.457437</v>
       </c>
       <c r="N23">
-        <v>142.0724465</v>
+        <v>141.142563</v>
       </c>
       <c r="O23">
-        <v>41.9113717175</v>
+        <v>41.637056085</v>
       </c>
       <c r="P23">
-        <v>100.1610747825</v>
+        <v>99.505506915</v>
       </c>
       <c r="Q23">
-        <v>192.3610747825</v>
+        <v>191.705506915</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1252600901496122</v>
+        <v>0.1260257177479918</v>
       </c>
       <c r="T23">
-        <v>1.229222323277573</v>
+        <v>1.24106633872575</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3339,7 +3339,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>8.275486225143359</v>
+        <v>7.899327760364116</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3347,22 +3347,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1065979098434336</v>
+        <v>0.1064493934686736</v>
       </c>
       <c r="C24">
-        <v>1515.599693589647</v>
+        <v>1502.787807458958</v>
       </c>
       <c r="D24">
-        <v>1865.881693589647</v>
+        <v>1870.450807458959</v>
       </c>
       <c r="E24">
-        <v>341.182</v>
+        <v>358.563</v>
       </c>
       <c r="F24">
-        <v>382.382</v>
+        <v>399.763</v>
       </c>
       <c r="G24">
         <v>32.1</v>
@@ -3383,45 +3383,45 @@
         <v>161.6</v>
       </c>
       <c r="M24">
-        <v>20.457437</v>
+        <v>21.7071309</v>
       </c>
       <c r="N24">
-        <v>141.142563</v>
+        <v>139.8928691</v>
       </c>
       <c r="O24">
-        <v>41.637056085</v>
+        <v>41.26839638449999</v>
       </c>
       <c r="P24">
-        <v>99.505506915</v>
+        <v>98.62447271549999</v>
       </c>
       <c r="Q24">
-        <v>191.705506915</v>
+        <v>190.8244727155</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1260257177479918</v>
+        <v>0.1268112317774981</v>
       </c>
       <c r="T24">
-        <v>1.24106633872575</v>
+        <v>1.253217990938815</v>
       </c>
       <c r="U24">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V24">
         <v>0.295</v>
       </c>
       <c r="W24">
-        <v>0.0377175</v>
+        <v>0.0382815</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y24">
-        <v>7.899327760364116</v>
+        <v>7.444558230401603</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3429,22 +3429,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1064493934686736</v>
+        <v>0.1061767970939135</v>
       </c>
       <c r="C25">
-        <v>1502.787807458958</v>
+        <v>1493.851742166032</v>
       </c>
       <c r="D25">
-        <v>1870.450807458959</v>
+        <v>1878.895742166033</v>
       </c>
       <c r="E25">
-        <v>358.563</v>
+        <v>375.9440000000001</v>
       </c>
       <c r="F25">
-        <v>399.763</v>
+        <v>417.1440000000001</v>
       </c>
       <c r="G25">
         <v>32.1</v>
@@ -3465,28 +3465,28 @@
         <v>161.6</v>
       </c>
       <c r="M25">
-        <v>21.7071309</v>
+        <v>22.6509192</v>
       </c>
       <c r="N25">
-        <v>139.8928691</v>
+        <v>138.9490808</v>
       </c>
       <c r="O25">
-        <v>41.26839638449999</v>
+        <v>40.98997883599999</v>
       </c>
       <c r="P25">
-        <v>98.62447271549999</v>
+        <v>97.959101964</v>
       </c>
       <c r="Q25">
-        <v>190.8244727155</v>
+        <v>190.159101964</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1268112317774981</v>
+        <v>0.1276174172288335</v>
       </c>
       <c r="T25">
-        <v>1.253217990938815</v>
+        <v>1.265689423473276</v>
       </c>
       <c r="U25">
         <v>0.0543</v>
@@ -3503,7 +3503,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>7.444558230401603</v>
+        <v>7.13436830413487</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1061767970939135</v>
+        <v>0.1059042007191534</v>
       </c>
       <c r="C26">
-        <v>1493.851742166032</v>
+        <v>1484.992279125817</v>
       </c>
       <c r="D26">
-        <v>1878.895742166033</v>
+        <v>1887.417279125817</v>
       </c>
       <c r="E26">
-        <v>375.944</v>
+        <v>393.325</v>
       </c>
       <c r="F26">
-        <v>417.144</v>
+        <v>434.525</v>
       </c>
       <c r="G26">
         <v>32.1</v>
@@ -3547,28 +3547,28 @@
         <v>161.6</v>
       </c>
       <c r="M26">
-        <v>22.6509192</v>
+        <v>23.5947075</v>
       </c>
       <c r="N26">
-        <v>138.9490808</v>
+        <v>138.0052925</v>
       </c>
       <c r="O26">
-        <v>40.98997883599999</v>
+        <v>40.7115612875</v>
       </c>
       <c r="P26">
-        <v>97.959101964</v>
+        <v>97.29373121250001</v>
       </c>
       <c r="Q26">
-        <v>190.159101964</v>
+        <v>189.4937312125</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1276174172288335</v>
+        <v>0.1284451009588712</v>
       </c>
       <c r="T26">
-        <v>1.265689423473276</v>
+        <v>1.27849342754199</v>
       </c>
       <c r="U26">
         <v>0.0543</v>
@@ -3585,7 +3585,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>7.134368304134871</v>
+        <v>6.848993571969476</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3593,22 +3593,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1059042007191534</v>
+        <v>0.1056316043443934</v>
       </c>
       <c r="C27">
-        <v>1484.992279125817</v>
+        <v>1476.210465351673</v>
       </c>
       <c r="D27">
-        <v>1887.417279125817</v>
+        <v>1896.016465351673</v>
       </c>
       <c r="E27">
-        <v>393.325</v>
+        <v>410.7060000000001</v>
       </c>
       <c r="F27">
-        <v>434.525</v>
+        <v>451.9060000000001</v>
       </c>
       <c r="G27">
         <v>32.1</v>
@@ -3629,28 +3629,28 @@
         <v>161.6</v>
       </c>
       <c r="M27">
-        <v>23.5947075</v>
+        <v>24.5384958</v>
       </c>
       <c r="N27">
-        <v>138.0052925</v>
+        <v>137.0615042</v>
       </c>
       <c r="O27">
-        <v>40.7115612875</v>
+        <v>40.433143739</v>
       </c>
       <c r="P27">
-        <v>97.29373121250001</v>
+        <v>96.628360461</v>
       </c>
       <c r="Q27">
-        <v>189.4937312125</v>
+        <v>188.828360461</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1284451009588712</v>
+        <v>0.1292951545194505</v>
       </c>
       <c r="T27">
-        <v>1.27849342754199</v>
+        <v>1.291643485774723</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>6.848993571969476</v>
+        <v>6.585570742278342</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3675,22 +3675,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1056316043443934</v>
+        <v>0.1053590079696333</v>
       </c>
       <c r="C28">
-        <v>1476.210465351673</v>
+        <v>1467.507367025317</v>
       </c>
       <c r="D28">
-        <v>1896.016465351673</v>
+        <v>1904.694367025317</v>
       </c>
       <c r="E28">
-        <v>410.7060000000001</v>
+        <v>428.0870000000001</v>
       </c>
       <c r="F28">
-        <v>451.9060000000001</v>
+        <v>469.2870000000001</v>
       </c>
       <c r="G28">
         <v>32.1</v>
@@ -3711,28 +3711,28 @@
         <v>161.6</v>
       </c>
       <c r="M28">
-        <v>24.5384958</v>
+        <v>25.4822841</v>
       </c>
       <c r="N28">
-        <v>137.0615042</v>
+        <v>136.1177159</v>
       </c>
       <c r="O28">
-        <v>40.433143739</v>
+        <v>40.15472619049999</v>
       </c>
       <c r="P28">
-        <v>96.628360461</v>
+        <v>95.96298970949999</v>
       </c>
       <c r="Q28">
-        <v>188.828360461</v>
+        <v>188.1629897095</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1292951545194505</v>
+        <v>0.1301684972186758</v>
       </c>
       <c r="T28">
-        <v>1.291643485774723</v>
+        <v>1.305153819575476</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3749,7 +3749,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>6.585570742278342</v>
+        <v>6.341660714786551</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3757,22 +3757,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1053590079696333</v>
+        <v>0.1050864115948733</v>
       </c>
       <c r="C29">
-        <v>1467.507367025317</v>
+        <v>1458.884069937495</v>
       </c>
       <c r="D29">
-        <v>1904.694367025317</v>
+        <v>1913.452069937495</v>
       </c>
       <c r="E29">
-        <v>428.0870000000001</v>
+        <v>445.4680000000001</v>
       </c>
       <c r="F29">
-        <v>469.2870000000001</v>
+        <v>486.6680000000001</v>
       </c>
       <c r="G29">
         <v>32.1</v>
@@ -3793,28 +3793,28 @@
         <v>161.6</v>
       </c>
       <c r="M29">
-        <v>25.4822841</v>
+        <v>26.4260724</v>
       </c>
       <c r="N29">
-        <v>136.1177159</v>
+        <v>135.1739276</v>
       </c>
       <c r="O29">
-        <v>40.15472619049999</v>
+        <v>39.87630864199999</v>
       </c>
       <c r="P29">
-        <v>95.96298970949999</v>
+        <v>95.29761895799999</v>
       </c>
       <c r="Q29">
-        <v>188.1629897095</v>
+        <v>187.497618958</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1301684972186758</v>
+        <v>0.131066099437324</v>
       </c>
       <c r="T29">
-        <v>1.305153819575476</v>
+        <v>1.31903944042625</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3831,7 +3831,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>6.341660714786551</v>
+        <v>6.115172832115603</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3839,22 +3839,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1050864115948733</v>
+        <v>0.1050182652201132</v>
       </c>
       <c r="C30">
-        <v>1458.884069937495</v>
+        <v>1443.705005798985</v>
       </c>
       <c r="D30">
-        <v>1913.452069937495</v>
+        <v>1915.654005798985</v>
       </c>
       <c r="E30">
-        <v>445.4680000000001</v>
+        <v>462.8490000000001</v>
       </c>
       <c r="F30">
-        <v>486.6680000000001</v>
+        <v>504.0490000000001</v>
       </c>
       <c r="G30">
         <v>32.1</v>
@@ -3875,45 +3875,45 @@
         <v>161.6</v>
       </c>
       <c r="M30">
-        <v>26.4260724</v>
+        <v>27.87390970000001</v>
       </c>
       <c r="N30">
-        <v>135.1739276</v>
+        <v>133.7260903</v>
       </c>
       <c r="O30">
-        <v>39.87630864199999</v>
+        <v>39.44919663849999</v>
       </c>
       <c r="P30">
-        <v>95.29761895799999</v>
+        <v>94.2768936615</v>
       </c>
       <c r="Q30">
-        <v>187.497618958</v>
+        <v>186.4768936615</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.131066099437324</v>
+        <v>0.1319889862255116</v>
       </c>
       <c r="T30">
-        <v>1.31903944042625</v>
+        <v>1.333316205526342</v>
       </c>
       <c r="U30">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V30">
         <v>0.295</v>
       </c>
       <c r="W30">
-        <v>0.0382815</v>
+        <v>0.03898650000000001</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y30">
-        <v>6.115172832115603</v>
+        <v>5.797536181298598</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3921,22 +3921,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1050182652201132</v>
+        <v>0.1047527188453531</v>
       </c>
       <c r="C31">
-        <v>1443.705005798985</v>
+        <v>1434.952869513802</v>
       </c>
       <c r="D31">
-        <v>1915.654005798985</v>
+        <v>1924.282869513802</v>
       </c>
       <c r="E31">
-        <v>462.849</v>
+        <v>480.2300000000001</v>
       </c>
       <c r="F31">
-        <v>504.049</v>
+        <v>521.4300000000001</v>
       </c>
       <c r="G31">
         <v>32.1</v>
@@ -3957,28 +3957,28 @@
         <v>161.6</v>
       </c>
       <c r="M31">
-        <v>27.8739097</v>
+        <v>28.835079</v>
       </c>
       <c r="N31">
-        <v>133.7260903</v>
+        <v>132.764921</v>
       </c>
       <c r="O31">
-        <v>39.4491966385</v>
+        <v>39.16565169499999</v>
       </c>
       <c r="P31">
-        <v>94.27689366150001</v>
+        <v>93.59926930499999</v>
       </c>
       <c r="Q31">
-        <v>186.4768936615</v>
+        <v>185.799269305</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1319889862255116</v>
+        <v>0.1329382412076474</v>
       </c>
       <c r="T31">
-        <v>1.333316205526342</v>
+        <v>1.348000878200722</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3995,7 +3995,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.7975361812986</v>
+        <v>5.604284975255312</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4003,22 +4003,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1047527188453531</v>
+        <v>0.1044871724705931</v>
       </c>
       <c r="C32">
-        <v>1434.952869513802</v>
+        <v>1426.278820598698</v>
       </c>
       <c r="D32">
-        <v>1924.282869513802</v>
+        <v>1932.989820598698</v>
       </c>
       <c r="E32">
-        <v>480.2300000000001</v>
+        <v>497.611</v>
       </c>
       <c r="F32">
-        <v>521.4300000000001</v>
+        <v>538.811</v>
       </c>
       <c r="G32">
         <v>32.1</v>
@@ -4039,28 +4039,28 @@
         <v>161.6</v>
       </c>
       <c r="M32">
-        <v>28.835079</v>
+        <v>29.7962483</v>
       </c>
       <c r="N32">
-        <v>132.764921</v>
+        <v>131.8037517</v>
       </c>
       <c r="O32">
-        <v>39.16565169499999</v>
+        <v>38.8821067515</v>
       </c>
       <c r="P32">
-        <v>93.59926930499999</v>
+        <v>92.92164494849999</v>
       </c>
       <c r="Q32">
-        <v>185.799269305</v>
+        <v>185.1216449485</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1329382412076474</v>
+        <v>0.1339150108269465</v>
       </c>
       <c r="T32">
-        <v>1.348000878200722</v>
+        <v>1.363111193561315</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -4077,7 +4077,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.604284975255312</v>
+        <v>5.423501588956754</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4085,22 +4085,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1044871724705931</v>
+        <v>0.104221626095833</v>
       </c>
       <c r="C33">
-        <v>1426.278820598698</v>
+        <v>1417.683923855497</v>
       </c>
       <c r="D33">
-        <v>1932.989820598698</v>
+        <v>1941.775923855497</v>
       </c>
       <c r="E33">
-        <v>497.611</v>
+        <v>514.992</v>
       </c>
       <c r="F33">
-        <v>538.811</v>
+        <v>556.192</v>
       </c>
       <c r="G33">
         <v>32.1</v>
@@ -4121,28 +4121,28 @@
         <v>161.6</v>
       </c>
       <c r="M33">
-        <v>29.7962483</v>
+        <v>30.7574176</v>
       </c>
       <c r="N33">
-        <v>131.8037517</v>
+        <v>130.8425824</v>
       </c>
       <c r="O33">
-        <v>38.8821067515</v>
+        <v>38.598561808</v>
       </c>
       <c r="P33">
-        <v>92.92164494849999</v>
+        <v>92.244020592</v>
       </c>
       <c r="Q33">
-        <v>185.1216449485</v>
+        <v>184.444020592</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1339150108269465</v>
+        <v>0.1349205089644603</v>
       </c>
       <c r="T33">
-        <v>1.363111193561315</v>
+        <v>1.378665929961927</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.423501588956754</v>
+        <v>5.254017164301856</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4167,22 +4167,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.104221626095833</v>
+        <v>0.103956079721073</v>
       </c>
       <c r="C34">
-        <v>1417.683923855497</v>
+        <v>1409.169263533983</v>
       </c>
       <c r="D34">
-        <v>1941.775923855497</v>
+        <v>1950.642263533983</v>
       </c>
       <c r="E34">
-        <v>514.992</v>
+        <v>532.373</v>
       </c>
       <c r="F34">
-        <v>556.192</v>
+        <v>573.5730000000001</v>
       </c>
       <c r="G34">
         <v>32.1</v>
@@ -4203,28 +4203,28 @@
         <v>161.6</v>
       </c>
       <c r="M34">
-        <v>30.7574176</v>
+        <v>31.71858690000001</v>
       </c>
       <c r="N34">
-        <v>130.8425824</v>
+        <v>129.8814131</v>
       </c>
       <c r="O34">
-        <v>38.598561808</v>
+        <v>38.31501686449999</v>
       </c>
       <c r="P34">
-        <v>92.244020592</v>
+        <v>91.56639623549998</v>
       </c>
       <c r="Q34">
-        <v>184.444020592</v>
+        <v>183.7663962355</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1349205089644603</v>
+        <v>0.1359560219717507</v>
       </c>
       <c r="T34">
-        <v>1.378665929961927</v>
+        <v>1.394684986852109</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4241,7 +4241,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.254017164301856</v>
+        <v>5.094804522959374</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4249,22 +4249,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.103956079721073</v>
+        <v>0.1036905333463129</v>
       </c>
       <c r="C35">
-        <v>1409.169263533983</v>
+        <v>1400.735943777944</v>
       </c>
       <c r="D35">
-        <v>1950.642263533983</v>
+        <v>1959.589943777944</v>
       </c>
       <c r="E35">
-        <v>532.373</v>
+        <v>549.754</v>
       </c>
       <c r="F35">
-        <v>573.5730000000001</v>
+        <v>590.9540000000001</v>
       </c>
       <c r="G35">
         <v>32.1</v>
@@ -4285,28 +4285,28 @@
         <v>161.6</v>
       </c>
       <c r="M35">
-        <v>31.71858690000001</v>
+        <v>32.67975620000001</v>
       </c>
       <c r="N35">
-        <v>129.8814131</v>
+        <v>128.9202438</v>
       </c>
       <c r="O35">
-        <v>38.31501686449999</v>
+        <v>38.03147192099999</v>
       </c>
       <c r="P35">
-        <v>91.56639623549998</v>
+        <v>90.88877187899999</v>
       </c>
       <c r="Q35">
-        <v>183.7663962355</v>
+        <v>183.088771879</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1359560219717507</v>
+        <v>0.1370229141610802</v>
       </c>
       <c r="T35">
-        <v>1.394684986852109</v>
+        <v>1.41118946970866</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4323,7 +4323,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.094804522959374</v>
+        <v>4.944957331107627</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4331,22 +4331,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1036905333463129</v>
+        <v>0.1034249869715528</v>
       </c>
       <c r="C36">
-        <v>1400.735943777944</v>
+        <v>1392.385089083546</v>
       </c>
       <c r="D36">
-        <v>1959.589943777944</v>
+        <v>1968.620089083546</v>
       </c>
       <c r="E36">
-        <v>549.754</v>
+        <v>567.1350000000001</v>
       </c>
       <c r="F36">
-        <v>590.9540000000001</v>
+        <v>608.3350000000002</v>
       </c>
       <c r="G36">
         <v>32.1</v>
@@ -4367,28 +4367,28 @@
         <v>161.6</v>
       </c>
       <c r="M36">
-        <v>32.67975620000001</v>
+        <v>33.64092550000001</v>
       </c>
       <c r="N36">
-        <v>128.9202438</v>
+        <v>127.9590745</v>
       </c>
       <c r="O36">
-        <v>38.03147192099999</v>
+        <v>37.74792697749999</v>
       </c>
       <c r="P36">
-        <v>90.88877187899999</v>
+        <v>90.2111475225</v>
       </c>
       <c r="Q36">
-        <v>183.088771879</v>
+        <v>182.4111475225</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1370229141610802</v>
+        <v>0.138122633802389</v>
       </c>
       <c r="T36">
-        <v>1.41118946970866</v>
+        <v>1.42820178280695</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4405,7 +4405,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>4.944957331107627</v>
+        <v>4.803672835933124</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4413,22 +4413,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1034249869715528</v>
+        <v>0.1031594405967928</v>
       </c>
       <c r="C37">
-        <v>1392.385089083546</v>
+        <v>1384.117844770438</v>
       </c>
       <c r="D37">
-        <v>1968.620089083546</v>
+        <v>1977.733844770438</v>
       </c>
       <c r="E37">
-        <v>567.1350000000001</v>
+        <v>584.5160000000001</v>
       </c>
       <c r="F37">
-        <v>608.3350000000002</v>
+        <v>625.7160000000001</v>
       </c>
       <c r="G37">
         <v>32.1</v>
@@ -4449,28 +4449,28 @@
         <v>161.6</v>
       </c>
       <c r="M37">
-        <v>33.64092550000001</v>
+        <v>34.60209480000001</v>
       </c>
       <c r="N37">
-        <v>127.9590745</v>
+        <v>126.9979052</v>
       </c>
       <c r="O37">
-        <v>37.74792697749999</v>
+        <v>37.464382034</v>
       </c>
       <c r="P37">
-        <v>90.2111475225</v>
+        <v>89.53352316599999</v>
       </c>
       <c r="Q37">
-        <v>182.4111475225</v>
+        <v>181.733523166</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.138122633802389</v>
+        <v>0.1392567196824888</v>
       </c>
       <c r="T37">
-        <v>1.42820178280695</v>
+        <v>1.445745730689563</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4487,7 +4487,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>4.803672835933124</v>
+        <v>4.670237479379426</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4495,22 +4495,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1031594405967928</v>
+        <v>0.1028938942220328</v>
       </c>
       <c r="C38">
-        <v>1384.117844770437</v>
+        <v>1375.935377466012</v>
       </c>
       <c r="D38">
-        <v>1977.733844770437</v>
+        <v>1986.932377466012</v>
       </c>
       <c r="E38">
-        <v>584.516</v>
+        <v>601.897</v>
       </c>
       <c r="F38">
-        <v>625.716</v>
+        <v>643.0970000000001</v>
       </c>
       <c r="G38">
         <v>32.1</v>
@@ -4531,28 +4531,28 @@
         <v>161.6</v>
       </c>
       <c r="M38">
-        <v>34.6020948</v>
+        <v>35.5632641</v>
       </c>
       <c r="N38">
-        <v>126.9979052</v>
+        <v>126.0367359</v>
       </c>
       <c r="O38">
-        <v>37.464382034</v>
+        <v>37.1808370905</v>
       </c>
       <c r="P38">
-        <v>89.53352316599999</v>
+        <v>88.85589880949999</v>
       </c>
       <c r="Q38">
-        <v>181.733523166</v>
+        <v>181.0558988095</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1392567196824888</v>
+        <v>0.1404268082889409</v>
       </c>
       <c r="T38">
-        <v>1.445745730689563</v>
+        <v>1.463846629298608</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4569,7 +4569,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.670237479379427</v>
+        <v>4.544014844801605</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1028938942220328</v>
+        <v>0.1032980978472727</v>
       </c>
       <c r="C39">
-        <v>1375.935377466012</v>
+        <v>1344.586519395096</v>
       </c>
       <c r="D39">
-        <v>1986.932377466012</v>
+        <v>1972.964519395096</v>
       </c>
       <c r="E39">
-        <v>601.897</v>
+        <v>619.278</v>
       </c>
       <c r="F39">
-        <v>643.0970000000001</v>
+        <v>660.4780000000001</v>
       </c>
       <c r="G39">
         <v>32.1</v>
@@ -4613,45 +4613,45 @@
         <v>161.6</v>
       </c>
       <c r="M39">
-        <v>35.5632641</v>
+        <v>38.17562840000001</v>
       </c>
       <c r="N39">
-        <v>126.0367359</v>
+        <v>123.4243716</v>
       </c>
       <c r="O39">
-        <v>37.1808370905</v>
+        <v>36.410189622</v>
       </c>
       <c r="P39">
-        <v>88.85589880949999</v>
+        <v>87.01418197799998</v>
       </c>
       <c r="Q39">
-        <v>181.0558988095</v>
+        <v>179.214181978</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1404268082889409</v>
+        <v>0.1416346416891495</v>
       </c>
       <c r="T39">
-        <v>1.463846629298608</v>
+        <v>1.482531427862783</v>
       </c>
       <c r="U39">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V39">
         <v>0.295</v>
       </c>
       <c r="W39">
-        <v>0.03898650000000001</v>
+        <v>0.04074900000000001</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y39">
-        <v>4.544014844801605</v>
+        <v>4.233067189013186</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4659,22 +4659,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1032980978472727</v>
+        <v>0.1030501764725126</v>
       </c>
       <c r="C40">
-        <v>1344.586519395096</v>
+        <v>1335.749424517136</v>
       </c>
       <c r="D40">
-        <v>1972.964519395096</v>
+        <v>1981.508424517136</v>
       </c>
       <c r="E40">
-        <v>619.278</v>
+        <v>636.659</v>
       </c>
       <c r="F40">
-        <v>660.4780000000001</v>
+        <v>677.859</v>
       </c>
       <c r="G40">
         <v>32.1</v>
@@ -4695,28 +4695,28 @@
         <v>161.6</v>
       </c>
       <c r="M40">
-        <v>38.17562840000001</v>
+        <v>39.1802502</v>
       </c>
       <c r="N40">
-        <v>123.4243716</v>
+        <v>122.4197498</v>
       </c>
       <c r="O40">
-        <v>36.410189622</v>
+        <v>36.11382619099999</v>
       </c>
       <c r="P40">
-        <v>87.01418197799998</v>
+        <v>86.30592360899999</v>
       </c>
       <c r="Q40">
-        <v>179.214181978</v>
+        <v>178.505923609</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1416346416891495</v>
+        <v>0.142882076184447</v>
       </c>
       <c r="T40">
-        <v>1.482531427862783</v>
+        <v>1.501828842773325</v>
       </c>
       <c r="U40">
         <v>0.0578</v>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.233067189013186</v>
+        <v>4.124527004679516</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4741,22 +4741,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1030501764725126</v>
+        <v>0.1028022550977526</v>
       </c>
       <c r="C41">
-        <v>1335.749424517136</v>
+        <v>1326.98665009194</v>
       </c>
       <c r="D41">
-        <v>1981.508424517136</v>
+        <v>1990.12665009194</v>
       </c>
       <c r="E41">
-        <v>636.659</v>
+        <v>654.0400000000001</v>
       </c>
       <c r="F41">
-        <v>677.859</v>
+        <v>695.2400000000001</v>
       </c>
       <c r="G41">
         <v>32.1</v>
@@ -4777,28 +4777,28 @@
         <v>161.6</v>
       </c>
       <c r="M41">
-        <v>39.1802502</v>
+        <v>40.18487200000001</v>
       </c>
       <c r="N41">
-        <v>122.4197498</v>
+        <v>121.415128</v>
       </c>
       <c r="O41">
-        <v>36.11382619099999</v>
+        <v>35.81746275999999</v>
       </c>
       <c r="P41">
-        <v>86.30592360899999</v>
+        <v>85.59766524</v>
       </c>
       <c r="Q41">
-        <v>178.505923609</v>
+        <v>177.79766524</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.142882076184447</v>
+        <v>0.1441710918295876</v>
       </c>
       <c r="T41">
-        <v>1.501828842773325</v>
+        <v>1.521769504847551</v>
       </c>
       <c r="U41">
         <v>0.0578</v>
@@ -4815,7 +4815,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.124527004679516</v>
+        <v>4.021413829562526</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4823,22 +4823,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1028022550977526</v>
+        <v>0.1035660087229925</v>
       </c>
       <c r="C42">
-        <v>1326.98665009194</v>
+        <v>1283.293178842921</v>
       </c>
       <c r="D42">
-        <v>1990.12665009194</v>
+        <v>1963.814178842921</v>
       </c>
       <c r="E42">
-        <v>654.0400000000001</v>
+        <v>671.421</v>
       </c>
       <c r="F42">
-        <v>695.2400000000001</v>
+        <v>712.6210000000001</v>
       </c>
       <c r="G42">
         <v>32.1</v>
@@ -4859,45 +4859,45 @@
         <v>161.6</v>
       </c>
       <c r="M42">
-        <v>40.18487200000001</v>
+        <v>43.6836673</v>
       </c>
       <c r="N42">
-        <v>121.415128</v>
+        <v>117.9163327</v>
       </c>
       <c r="O42">
-        <v>35.81746275999999</v>
+        <v>34.7853181465</v>
       </c>
       <c r="P42">
-        <v>85.59766524</v>
+        <v>83.13101455349999</v>
       </c>
       <c r="Q42">
-        <v>177.79766524</v>
+        <v>175.3310145535</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1441710918295876</v>
+        <v>0.1455038029203263</v>
       </c>
       <c r="T42">
-        <v>1.521769504847551</v>
+        <v>1.542386121568361</v>
       </c>
       <c r="U42">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V42">
         <v>0.295</v>
       </c>
       <c r="W42">
-        <v>0.04074900000000001</v>
+        <v>0.0432165</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y42">
-        <v>4.021413829562526</v>
+        <v>3.699323110630869</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4905,22 +4905,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1035660087229925</v>
+        <v>0.1033427623482325</v>
       </c>
       <c r="C43">
-        <v>1283.293178842921</v>
+        <v>1273.531110889941</v>
       </c>
       <c r="D43">
-        <v>1963.814178842921</v>
+        <v>1971.433110889942</v>
       </c>
       <c r="E43">
-        <v>671.421</v>
+        <v>688.8020000000001</v>
       </c>
       <c r="F43">
-        <v>712.6210000000001</v>
+        <v>730.0020000000002</v>
       </c>
       <c r="G43">
         <v>32.1</v>
@@ -4941,28 +4941,28 @@
         <v>161.6</v>
       </c>
       <c r="M43">
-        <v>43.6836673</v>
+        <v>44.74912260000001</v>
       </c>
       <c r="N43">
-        <v>117.9163327</v>
+        <v>116.8508774</v>
       </c>
       <c r="O43">
-        <v>34.7853181465</v>
+        <v>34.47100883299999</v>
       </c>
       <c r="P43">
-        <v>83.13101455349999</v>
+        <v>82.37986856699999</v>
       </c>
       <c r="Q43">
-        <v>175.3310145535</v>
+        <v>174.579868567</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1455038029203263</v>
+        <v>0.1468824695659181</v>
       </c>
       <c r="T43">
-        <v>1.542386121568361</v>
+        <v>1.56371365610713</v>
       </c>
       <c r="U43">
         <v>0.0613</v>
@@ -4979,7 +4979,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.699323110630869</v>
+        <v>3.611243988949181</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4987,22 +4987,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1033427623482325</v>
+        <v>0.1031195159734724</v>
       </c>
       <c r="C44">
-        <v>1273.531110889941</v>
+        <v>1263.828390924472</v>
       </c>
       <c r="D44">
-        <v>1971.433110889942</v>
+        <v>1979.111390924473</v>
       </c>
       <c r="E44">
-        <v>688.802</v>
+        <v>706.183</v>
       </c>
       <c r="F44">
-        <v>730.0020000000001</v>
+        <v>747.383</v>
       </c>
       <c r="G44">
         <v>32.1</v>
@@ -5023,28 +5023,28 @@
         <v>161.6</v>
       </c>
       <c r="M44">
-        <v>44.74912260000001</v>
+        <v>45.8145779</v>
       </c>
       <c r="N44">
-        <v>116.8508774</v>
+        <v>115.7854221</v>
       </c>
       <c r="O44">
-        <v>34.47100883299999</v>
+        <v>34.15669951949999</v>
       </c>
       <c r="P44">
-        <v>82.37986856699999</v>
+        <v>81.6287225805</v>
       </c>
       <c r="Q44">
-        <v>174.579868567</v>
+        <v>173.8287225805</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1468824695659181</v>
+        <v>0.1483095104797762</v>
       </c>
       <c r="T44">
-        <v>1.56371365610713</v>
+        <v>1.585789525191119</v>
       </c>
       <c r="U44">
         <v>0.0613</v>
@@ -5061,7 +5061,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.611243988949182</v>
+        <v>3.527261570601526</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5069,22 +5069,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1031195159734724</v>
+        <v>0.1037648295987124</v>
       </c>
       <c r="C45">
-        <v>1263.828390924472</v>
+        <v>1224.414245044933</v>
       </c>
       <c r="D45">
-        <v>1979.111390924473</v>
+        <v>1957.078245044933</v>
       </c>
       <c r="E45">
-        <v>706.183</v>
+        <v>723.564</v>
       </c>
       <c r="F45">
-        <v>747.383</v>
+        <v>764.764</v>
       </c>
       <c r="G45">
         <v>32.1</v>
@@ -5105,45 +5105,45 @@
         <v>161.6</v>
       </c>
       <c r="M45">
-        <v>45.8145779</v>
+        <v>49.0213724</v>
       </c>
       <c r="N45">
-        <v>115.7854221</v>
+        <v>112.5786276</v>
       </c>
       <c r="O45">
-        <v>34.15669951949999</v>
+        <v>33.210695142</v>
       </c>
       <c r="P45">
-        <v>81.6287225805</v>
+        <v>79.36793245799998</v>
       </c>
       <c r="Q45">
-        <v>173.8287225805</v>
+        <v>171.567932458</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1483095104797762</v>
+        <v>0.1497875171405578</v>
       </c>
       <c r="T45">
-        <v>1.585789525191119</v>
+        <v>1.608653818170965</v>
       </c>
       <c r="U45">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V45">
         <v>0.295</v>
       </c>
       <c r="W45">
-        <v>0.0432165</v>
+        <v>0.04519050000000001</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y45">
-        <v>3.527261570601526</v>
+        <v>3.296521335253356</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5151,22 +5151,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1037648295987124</v>
+        <v>0.1035613232239523</v>
       </c>
       <c r="C46">
-        <v>1224.414245044933</v>
+        <v>1213.92848006624</v>
       </c>
       <c r="D46">
-        <v>1957.078245044933</v>
+        <v>1963.97348006624</v>
       </c>
       <c r="E46">
-        <v>723.564</v>
+        <v>740.9450000000001</v>
       </c>
       <c r="F46">
-        <v>764.764</v>
+        <v>782.1450000000001</v>
       </c>
       <c r="G46">
         <v>32.1</v>
@@ -5187,28 +5187,28 @@
         <v>161.6</v>
       </c>
       <c r="M46">
-        <v>49.0213724</v>
+        <v>50.13549450000001</v>
       </c>
       <c r="N46">
-        <v>112.5786276</v>
+        <v>111.4645055</v>
       </c>
       <c r="O46">
-        <v>33.210695142</v>
+        <v>32.88202912249999</v>
       </c>
       <c r="P46">
-        <v>79.36793245799998</v>
+        <v>78.5824763775</v>
       </c>
       <c r="Q46">
-        <v>171.567932458</v>
+        <v>170.7824763775</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1497875171405578</v>
+        <v>0.1513192694980951</v>
       </c>
       <c r="T46">
-        <v>1.608653818170965</v>
+        <v>1.632349539986442</v>
       </c>
       <c r="U46">
         <v>0.0641</v>
@@ -5225,7 +5225,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.296521335253356</v>
+        <v>3.223265305581058</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5233,22 +5233,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1035613232239523</v>
+        <v>0.1033578168491922</v>
       </c>
       <c r="C47">
-        <v>1213.92848006624</v>
+        <v>1203.491473861216</v>
       </c>
       <c r="D47">
-        <v>1963.97348006624</v>
+        <v>1970.917473861217</v>
       </c>
       <c r="E47">
-        <v>740.9450000000001</v>
+        <v>758.326</v>
       </c>
       <c r="F47">
-        <v>782.1450000000001</v>
+        <v>799.5260000000001</v>
       </c>
       <c r="G47">
         <v>32.1</v>
@@ -5269,28 +5269,28 @@
         <v>161.6</v>
       </c>
       <c r="M47">
-        <v>50.13549450000001</v>
+        <v>51.24961660000001</v>
       </c>
       <c r="N47">
-        <v>111.4645055</v>
+        <v>110.3503834</v>
       </c>
       <c r="O47">
-        <v>32.88202912249999</v>
+        <v>32.553363103</v>
       </c>
       <c r="P47">
-        <v>78.5824763775</v>
+        <v>77.79702029699999</v>
       </c>
       <c r="Q47">
-        <v>170.7824763775</v>
+        <v>169.997020297</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1513192694980951</v>
+        <v>0.1529077534244301</v>
       </c>
       <c r="T47">
-        <v>1.632349539986442</v>
+        <v>1.656922881128418</v>
       </c>
       <c r="U47">
         <v>0.0641</v>
@@ -5307,7 +5307,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.223265305581058</v>
+        <v>3.153194320677122</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5315,22 +5315,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1033578168491922</v>
+        <v>0.1031543104744322</v>
       </c>
       <c r="C48">
-        <v>1203.491473861216</v>
+        <v>1193.10374545212</v>
       </c>
       <c r="D48">
-        <v>1970.917473861217</v>
+        <v>1977.910745452121</v>
       </c>
       <c r="E48">
-        <v>758.326</v>
+        <v>775.7070000000001</v>
       </c>
       <c r="F48">
-        <v>799.5260000000001</v>
+        <v>816.9070000000002</v>
       </c>
       <c r="G48">
         <v>32.1</v>
@@ -5351,28 +5351,28 @@
         <v>161.6</v>
       </c>
       <c r="M48">
-        <v>51.24961660000001</v>
+        <v>52.36373870000001</v>
       </c>
       <c r="N48">
-        <v>110.3503834</v>
+        <v>109.2362613</v>
       </c>
       <c r="O48">
-        <v>32.553363103</v>
+        <v>32.22469708349999</v>
       </c>
       <c r="P48">
-        <v>77.79702029699999</v>
+        <v>77.01156421649999</v>
       </c>
       <c r="Q48">
-        <v>169.997020297</v>
+        <v>169.2115642165</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1529077534244301</v>
+        <v>0.1545561801404381</v>
       </c>
       <c r="T48">
-        <v>1.656922881128418</v>
+        <v>1.682423518162544</v>
       </c>
       <c r="U48">
         <v>0.0641</v>
@@ -5389,7 +5389,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.153194320677122</v>
+        <v>3.086105079811651</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5397,22 +5397,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1031543104744322</v>
+        <v>0.1029508040996721</v>
       </c>
       <c r="C49">
-        <v>1193.10374545212</v>
+        <v>1182.765821253888</v>
       </c>
       <c r="D49">
-        <v>1977.910745452121</v>
+        <v>1984.953821253888</v>
       </c>
       <c r="E49">
-        <v>775.7070000000001</v>
+        <v>793.0880000000001</v>
       </c>
       <c r="F49">
-        <v>816.9070000000002</v>
+        <v>834.2880000000001</v>
       </c>
       <c r="G49">
         <v>32.1</v>
@@ -5433,28 +5433,28 @@
         <v>161.6</v>
       </c>
       <c r="M49">
-        <v>52.36373870000001</v>
+        <v>53.47786080000001</v>
       </c>
       <c r="N49">
-        <v>109.2362613</v>
+        <v>108.1221392</v>
       </c>
       <c r="O49">
-        <v>32.22469708349999</v>
+        <v>31.896031064</v>
       </c>
       <c r="P49">
-        <v>77.01156421649999</v>
+        <v>76.22610813599999</v>
       </c>
       <c r="Q49">
-        <v>169.2115642165</v>
+        <v>168.426108136</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1545561801404381</v>
+        <v>0.1562680078839848</v>
       </c>
       <c r="T49">
-        <v>1.682423518162544</v>
+        <v>1.708904948928751</v>
       </c>
       <c r="U49">
         <v>0.0641</v>
@@ -5471,7 +5471,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.086105079811651</v>
+        <v>3.021811223982242</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5479,22 +5479,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1029508040996721</v>
+        <v>0.1054418077249121</v>
       </c>
       <c r="C50">
-        <v>1182.765821253888</v>
+        <v>1082.481110697643</v>
       </c>
       <c r="D50">
-        <v>1984.953821253888</v>
+        <v>1902.050110697643</v>
       </c>
       <c r="E50">
-        <v>793.088</v>
+        <v>810.4690000000001</v>
       </c>
       <c r="F50">
-        <v>834.288</v>
+        <v>851.6690000000001</v>
       </c>
       <c r="G50">
         <v>32.1</v>
@@ -5515,45 +5515,45 @@
         <v>161.6</v>
       </c>
       <c r="M50">
-        <v>53.4778608</v>
+        <v>61.23500110000001</v>
       </c>
       <c r="N50">
-        <v>108.1221392</v>
+        <v>100.3649989</v>
       </c>
       <c r="O50">
-        <v>31.896031064</v>
+        <v>29.6076746755</v>
       </c>
       <c r="P50">
-        <v>76.22610813599999</v>
+        <v>70.7573242245</v>
       </c>
       <c r="Q50">
-        <v>168.426108136</v>
+        <v>162.9573242245</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1562680078839848</v>
+        <v>0.1580469661272786</v>
       </c>
       <c r="T50">
-        <v>1.708904948928751</v>
+        <v>1.736424867175987</v>
       </c>
       <c r="U50">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V50">
         <v>0.295</v>
       </c>
       <c r="W50">
-        <v>0.04519050000000001</v>
+        <v>0.05068950000000001</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y50">
-        <v>3.021811223982243</v>
+        <v>2.639013588586348</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5561,22 +5561,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1054418077249121</v>
+        <v>0.105293291350152</v>
       </c>
       <c r="C51">
-        <v>1082.481110697643</v>
+        <v>1069.848302983562</v>
       </c>
       <c r="D51">
-        <v>1902.050110697643</v>
+        <v>1906.798302983563</v>
       </c>
       <c r="E51">
-        <v>810.4690000000001</v>
+        <v>827.85</v>
       </c>
       <c r="F51">
-        <v>851.6690000000001</v>
+        <v>869.0500000000001</v>
       </c>
       <c r="G51">
         <v>32.1</v>
@@ -5597,28 +5597,28 @@
         <v>161.6</v>
       </c>
       <c r="M51">
-        <v>61.23500110000001</v>
+        <v>62.48469500000001</v>
       </c>
       <c r="N51">
-        <v>100.3649989</v>
+        <v>99.11530499999998</v>
       </c>
       <c r="O51">
-        <v>29.6076746755</v>
+        <v>29.23901497499999</v>
       </c>
       <c r="P51">
-        <v>70.7573242245</v>
+        <v>69.87629002499999</v>
       </c>
       <c r="Q51">
-        <v>162.9573242245</v>
+        <v>162.076290025</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1580469661272786</v>
+        <v>0.159897082700304</v>
       </c>
       <c r="T51">
-        <v>1.736424867175987</v>
+        <v>1.765045582153111</v>
       </c>
       <c r="U51">
         <v>0.07190000000000001</v>
@@ -5635,7 +5635,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.639013588586348</v>
+        <v>2.586233316814621</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.105293291350152</v>
+        <v>0.105144774975392</v>
       </c>
       <c r="C52">
-        <v>1069.848302983562</v>
+        <v>1057.23926094406</v>
       </c>
       <c r="D52">
-        <v>1906.798302983563</v>
+        <v>1911.57026094406</v>
       </c>
       <c r="E52">
-        <v>827.85</v>
+        <v>845.231</v>
       </c>
       <c r="F52">
-        <v>869.0500000000001</v>
+        <v>886.431</v>
       </c>
       <c r="G52">
         <v>32.1</v>
@@ -5679,28 +5679,28 @@
         <v>161.6</v>
       </c>
       <c r="M52">
-        <v>62.48469500000001</v>
+        <v>63.73438890000001</v>
       </c>
       <c r="N52">
-        <v>99.11530499999998</v>
+        <v>97.8656111</v>
       </c>
       <c r="O52">
-        <v>29.23901497499999</v>
+        <v>28.8703552745</v>
       </c>
       <c r="P52">
-        <v>69.87629002499999</v>
+        <v>68.9952558255</v>
       </c>
       <c r="Q52">
-        <v>162.076290025</v>
+        <v>161.1952558255</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.159897082700304</v>
+        <v>0.1618227142354938</v>
       </c>
       <c r="T52">
-        <v>1.765045582153111</v>
+        <v>1.794834489578282</v>
       </c>
       <c r="U52">
         <v>0.07190000000000001</v>
@@ -5717,7 +5717,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.586233316814621</v>
+        <v>2.535522859622178</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5725,22 +5725,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.105144774975392</v>
+        <v>0.1064259986006319</v>
       </c>
       <c r="C53">
-        <v>1057.23926094406</v>
+        <v>999.4605926802985</v>
       </c>
       <c r="D53">
-        <v>1911.57026094406</v>
+        <v>1871.172592680299</v>
       </c>
       <c r="E53">
-        <v>845.231</v>
+        <v>862.6120000000001</v>
       </c>
       <c r="F53">
-        <v>886.431</v>
+        <v>903.8120000000001</v>
       </c>
       <c r="G53">
         <v>32.1</v>
@@ -5761,45 +5761,45 @@
         <v>161.6</v>
       </c>
       <c r="M53">
-        <v>63.73438890000001</v>
+        <v>68.50894960000001</v>
       </c>
       <c r="N53">
-        <v>97.8656111</v>
+        <v>93.09105039999999</v>
       </c>
       <c r="O53">
-        <v>28.8703552745</v>
+        <v>27.46185986799999</v>
       </c>
       <c r="P53">
-        <v>68.9952558255</v>
+        <v>65.629190532</v>
       </c>
       <c r="Q53">
-        <v>161.1952558255</v>
+        <v>157.829190532</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1618227142354938</v>
+        <v>0.1638285804179831</v>
       </c>
       <c r="T53">
-        <v>1.794834489578282</v>
+        <v>1.825864601479502</v>
       </c>
       <c r="U53">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V53">
         <v>0.295</v>
       </c>
       <c r="W53">
-        <v>0.05068950000000001</v>
+        <v>0.05343900000000001</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y53">
-        <v>2.535522859622178</v>
+        <v>2.358815905710514</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5807,22 +5807,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1064259986006319</v>
+        <v>0.1063049772258719</v>
       </c>
       <c r="C54">
-        <v>999.4605926802985</v>
+        <v>985.8222910492956</v>
       </c>
       <c r="D54">
-        <v>1871.172592680299</v>
+        <v>1874.915291049296</v>
       </c>
       <c r="E54">
-        <v>862.6120000000001</v>
+        <v>879.9930000000001</v>
       </c>
       <c r="F54">
-        <v>903.8120000000001</v>
+        <v>921.1930000000001</v>
       </c>
       <c r="G54">
         <v>32.1</v>
@@ -5843,28 +5843,28 @@
         <v>161.6</v>
       </c>
       <c r="M54">
-        <v>68.50894960000001</v>
+        <v>69.82642940000001</v>
       </c>
       <c r="N54">
-        <v>93.09105039999999</v>
+        <v>91.77357059999999</v>
       </c>
       <c r="O54">
-        <v>27.46185986799999</v>
+        <v>27.07320332699999</v>
       </c>
       <c r="P54">
-        <v>65.629190532</v>
+        <v>64.70036727299998</v>
       </c>
       <c r="Q54">
-        <v>157.829190532</v>
+        <v>156.900367273</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1638285804179831</v>
+        <v>0.165919802608238</v>
       </c>
       <c r="T54">
-        <v>1.825864601479502</v>
+        <v>1.858215143674391</v>
       </c>
       <c r="U54">
         <v>0.07580000000000001</v>
@@ -5881,7 +5881,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.358815905710514</v>
+        <v>2.31430994522541</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5889,22 +5889,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1063049772258719</v>
+        <v>0.1061839558511118</v>
       </c>
       <c r="C55">
-        <v>985.8222910492956</v>
+        <v>972.1989916318965</v>
       </c>
       <c r="D55">
-        <v>1874.915291049296</v>
+        <v>1878.672991631897</v>
       </c>
       <c r="E55">
-        <v>879.9930000000001</v>
+        <v>897.3740000000001</v>
       </c>
       <c r="F55">
-        <v>921.1930000000001</v>
+        <v>938.5740000000002</v>
       </c>
       <c r="G55">
         <v>32.1</v>
@@ -5925,28 +5925,28 @@
         <v>161.6</v>
       </c>
       <c r="M55">
-        <v>69.82642940000001</v>
+        <v>71.14390920000002</v>
       </c>
       <c r="N55">
-        <v>91.77357059999999</v>
+        <v>90.45609079999997</v>
       </c>
       <c r="O55">
-        <v>27.07320332699999</v>
+        <v>26.68454678599999</v>
       </c>
       <c r="P55">
-        <v>64.70036727299998</v>
+        <v>63.77154401399998</v>
       </c>
       <c r="Q55">
-        <v>156.900367273</v>
+        <v>155.971544014</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.165919802608238</v>
+        <v>0.1681019475024169</v>
       </c>
       <c r="T55">
-        <v>1.858215143674391</v>
+        <v>1.8919722311821</v>
       </c>
       <c r="U55">
         <v>0.07580000000000001</v>
@@ -5963,7 +5963,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.31430994522541</v>
+        <v>2.271452353647161</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5971,22 +5971,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1061839558511118</v>
+        <v>0.1060629344763517</v>
       </c>
       <c r="C56">
-        <v>972.1989916318965</v>
+        <v>958.5907848114437</v>
       </c>
       <c r="D56">
-        <v>1878.672991631897</v>
+        <v>1882.445784811444</v>
       </c>
       <c r="E56">
-        <v>897.3740000000001</v>
+        <v>914.7550000000001</v>
       </c>
       <c r="F56">
-        <v>938.5740000000002</v>
+        <v>955.9550000000002</v>
       </c>
       <c r="G56">
         <v>32.1</v>
@@ -6007,28 +6007,28 @@
         <v>161.6</v>
       </c>
       <c r="M56">
-        <v>71.14390920000002</v>
+        <v>72.46138900000001</v>
       </c>
       <c r="N56">
-        <v>90.45609079999997</v>
+        <v>89.13861099999998</v>
       </c>
       <c r="O56">
-        <v>26.68454678599999</v>
+        <v>26.295890245</v>
       </c>
       <c r="P56">
-        <v>63.77154401399998</v>
+        <v>62.84272075499999</v>
       </c>
       <c r="Q56">
-        <v>155.971544014</v>
+        <v>155.042720755</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1681019475024169</v>
+        <v>0.170381076614115</v>
       </c>
       <c r="T56">
-        <v>1.8919722311821</v>
+        <v>1.927229633690152</v>
       </c>
       <c r="U56">
         <v>0.07580000000000001</v>
@@ -6045,7 +6045,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.271452353647161</v>
+        <v>2.230153219944486</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6053,22 +6053,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1060629344763517</v>
+        <v>0.1059419131015917</v>
       </c>
       <c r="C57">
-        <v>958.5907848114437</v>
+        <v>944.9977616987823</v>
       </c>
       <c r="D57">
-        <v>1882.445784811444</v>
+        <v>1886.233761698782</v>
       </c>
       <c r="E57">
-        <v>914.7550000000001</v>
+        <v>932.1360000000001</v>
       </c>
       <c r="F57">
-        <v>955.9550000000002</v>
+        <v>973.3360000000001</v>
       </c>
       <c r="G57">
         <v>32.1</v>
@@ -6089,28 +6089,28 @@
         <v>161.6</v>
       </c>
       <c r="M57">
-        <v>72.46138900000001</v>
+        <v>73.77886880000001</v>
       </c>
       <c r="N57">
-        <v>89.13861099999998</v>
+        <v>87.82113119999998</v>
       </c>
       <c r="O57">
-        <v>26.295890245</v>
+        <v>25.90723370399999</v>
       </c>
       <c r="P57">
-        <v>62.84272075499999</v>
+        <v>61.91389749599999</v>
       </c>
       <c r="Q57">
-        <v>155.042720755</v>
+        <v>154.113897496</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.170381076614115</v>
+        <v>0.1727638025036174</v>
       </c>
       <c r="T57">
-        <v>1.927229633690152</v>
+        <v>1.964089645403116</v>
       </c>
       <c r="U57">
         <v>0.07580000000000001</v>
@@ -6127,7 +6127,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.230153219944486</v>
+        <v>2.19032905530262</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6135,22 +6135,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1059419131015917</v>
+        <v>0.1058208917268316</v>
       </c>
       <c r="C58">
-        <v>944.9977616987823</v>
+        <v>931.4200141395914</v>
       </c>
       <c r="D58">
-        <v>1886.233761698782</v>
+        <v>1890.037014139592</v>
       </c>
       <c r="E58">
-        <v>932.1360000000001</v>
+        <v>949.5170000000002</v>
       </c>
       <c r="F58">
-        <v>973.3360000000001</v>
+        <v>990.7170000000002</v>
       </c>
       <c r="G58">
         <v>32.1</v>
@@ -6171,28 +6171,28 @@
         <v>161.6</v>
       </c>
       <c r="M58">
-        <v>73.77886880000001</v>
+        <v>75.09634860000003</v>
       </c>
       <c r="N58">
-        <v>87.82113119999998</v>
+        <v>86.50365139999997</v>
       </c>
       <c r="O58">
-        <v>25.90723370399999</v>
+        <v>25.51857716299999</v>
       </c>
       <c r="P58">
-        <v>61.91389749599999</v>
+        <v>60.98507423699998</v>
       </c>
       <c r="Q58">
-        <v>154.113897496</v>
+        <v>153.185074237</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1727638025036174</v>
+        <v>0.1752573528530968</v>
       </c>
       <c r="T58">
-        <v>1.964089645403116</v>
+        <v>2.00266407626552</v>
       </c>
       <c r="U58">
         <v>0.07580000000000001</v>
@@ -6209,7 +6209,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.19032905530262</v>
+        <v>2.151902229770995</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6217,22 +6217,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1058208917268316</v>
+        <v>0.1056998703520716</v>
       </c>
       <c r="C59">
-        <v>931.4200141395914</v>
+        <v>917.8576347218086</v>
       </c>
       <c r="D59">
-        <v>1890.037014139592</v>
+        <v>1893.855634721809</v>
       </c>
       <c r="E59">
-        <v>949.5170000000002</v>
+        <v>966.8980000000001</v>
       </c>
       <c r="F59">
-        <v>990.7170000000002</v>
+        <v>1008.098</v>
       </c>
       <c r="G59">
         <v>32.1</v>
@@ -6253,28 +6253,28 @@
         <v>161.6</v>
       </c>
       <c r="M59">
-        <v>75.09634860000003</v>
+        <v>76.41382840000001</v>
       </c>
       <c r="N59">
-        <v>86.50365139999997</v>
+        <v>85.18617159999998</v>
       </c>
       <c r="O59">
-        <v>25.51857716299999</v>
+        <v>25.12992062199999</v>
       </c>
       <c r="P59">
-        <v>60.98507423699998</v>
+        <v>60.05625097799999</v>
       </c>
       <c r="Q59">
-        <v>153.185074237</v>
+        <v>152.256250978</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1752573528530968</v>
+        <v>0.1778696436954085</v>
       </c>
       <c r="T59">
-        <v>2.00266407626552</v>
+        <v>2.043075384788039</v>
       </c>
       <c r="U59">
         <v>0.07580000000000001</v>
@@ -6291,7 +6291,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.151902229770995</v>
+        <v>2.114800467188737</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6299,22 +6299,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1056998703520716</v>
+        <v>0.1055788489773115</v>
       </c>
       <c r="C60">
-        <v>917.8576347218088</v>
+        <v>904.3107167831429</v>
       </c>
       <c r="D60">
-        <v>1893.855634721809</v>
+        <v>1897.689716783143</v>
       </c>
       <c r="E60">
-        <v>966.8979999999999</v>
+        <v>984.279</v>
       </c>
       <c r="F60">
-        <v>1008.098</v>
+        <v>1025.479</v>
       </c>
       <c r="G60">
         <v>32.1</v>
@@ -6335,28 +6335,28 @@
         <v>161.6</v>
       </c>
       <c r="M60">
-        <v>76.4138284</v>
+        <v>77.73130820000002</v>
       </c>
       <c r="N60">
-        <v>85.18617159999999</v>
+        <v>83.86869179999998</v>
       </c>
       <c r="O60">
-        <v>25.129920622</v>
+        <v>24.74126408099999</v>
       </c>
       <c r="P60">
-        <v>60.05625097799999</v>
+        <v>59.12742771899998</v>
       </c>
       <c r="Q60">
-        <v>152.256250978</v>
+        <v>151.327427719</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1778696436954085</v>
+        <v>0.1806093633592964</v>
       </c>
       <c r="T60">
-        <v>2.043075384788038</v>
+        <v>2.085457976653119</v>
       </c>
       <c r="U60">
         <v>0.07580000000000001</v>
@@ -6373,7 +6373,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.114800467188737</v>
+        <v>2.078956391473674</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6381,22 +6381,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1055788489773115</v>
+        <v>0.1054578276025515</v>
       </c>
       <c r="C61">
-        <v>904.3107167831429</v>
+        <v>890.7793544186788</v>
       </c>
       <c r="D61">
-        <v>1897.689716783143</v>
+        <v>1901.539354418679</v>
       </c>
       <c r="E61">
-        <v>984.279</v>
+        <v>1001.66</v>
       </c>
       <c r="F61">
-        <v>1025.479</v>
+        <v>1042.86</v>
       </c>
       <c r="G61">
         <v>32.1</v>
@@ -6417,28 +6417,28 @@
         <v>161.6</v>
       </c>
       <c r="M61">
-        <v>77.73130820000002</v>
+        <v>79.04878800000002</v>
       </c>
       <c r="N61">
-        <v>83.86869179999998</v>
+        <v>82.55121199999998</v>
       </c>
       <c r="O61">
-        <v>24.74126408099999</v>
+        <v>24.35260753999999</v>
       </c>
       <c r="P61">
-        <v>59.12742771899998</v>
+        <v>58.19860445999998</v>
       </c>
       <c r="Q61">
-        <v>151.327427719</v>
+        <v>150.39860446</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1806093633592964</v>
+        <v>0.1834860690063786</v>
       </c>
       <c r="T61">
-        <v>2.085457976653119</v>
+        <v>2.129959698111453</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6455,7 +6455,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.078956391473674</v>
+        <v>2.044307118282445</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6463,22 +6463,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1054578276025515</v>
+        <v>0.1053368062277914</v>
       </c>
       <c r="C62">
-        <v>890.7793544186788</v>
+        <v>877.2636424885768</v>
       </c>
       <c r="D62">
-        <v>1901.539354418679</v>
+        <v>1905.404642488577</v>
       </c>
       <c r="E62">
-        <v>1001.66</v>
+        <v>1019.041</v>
       </c>
       <c r="F62">
-        <v>1042.86</v>
+        <v>1060.241</v>
       </c>
       <c r="G62">
         <v>32.1</v>
@@ -6499,28 +6499,28 @@
         <v>161.6</v>
       </c>
       <c r="M62">
-        <v>79.04878800000002</v>
+        <v>80.3662678</v>
       </c>
       <c r="N62">
-        <v>82.55121199999998</v>
+        <v>81.23373219999999</v>
       </c>
       <c r="O62">
-        <v>24.35260753999999</v>
+        <v>23.963950999</v>
       </c>
       <c r="P62">
-        <v>58.19860445999998</v>
+        <v>57.26978120099999</v>
       </c>
       <c r="Q62">
-        <v>150.39860446</v>
+        <v>149.469781201</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1834860690063786</v>
+        <v>0.1865102980199779</v>
       </c>
       <c r="T62">
-        <v>2.129959698111453</v>
+        <v>2.176743559131753</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -6537,7 +6537,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.044307118282445</v>
+        <v>2.010793886835192</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6545,22 +6545,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1053368062277914</v>
+        <v>0.1114226048530313</v>
       </c>
       <c r="C63">
-        <v>877.2636424885768</v>
+        <v>683.17662815475</v>
       </c>
       <c r="D63">
-        <v>1905.404642488577</v>
+        <v>1728.69862815475</v>
       </c>
       <c r="E63">
-        <v>1019.041</v>
+        <v>1036.422</v>
       </c>
       <c r="F63">
-        <v>1060.241</v>
+        <v>1077.622</v>
       </c>
       <c r="G63">
         <v>32.1</v>
@@ -6581,45 +6581,45 @@
         <v>161.6</v>
       </c>
       <c r="M63">
-        <v>80.3662678</v>
+        <v>96.98598</v>
       </c>
       <c r="N63">
-        <v>81.23373219999999</v>
+        <v>64.61402</v>
       </c>
       <c r="O63">
-        <v>23.963950999</v>
+        <v>19.0611359</v>
       </c>
       <c r="P63">
-        <v>57.26978120099999</v>
+        <v>45.5528841</v>
       </c>
       <c r="Q63">
-        <v>149.469781201</v>
+        <v>137.7528841</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1865102980199779</v>
+        <v>0.1896936969816614</v>
       </c>
       <c r="T63">
-        <v>2.176743559131753</v>
+        <v>2.225989728626806</v>
       </c>
       <c r="U63">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V63">
         <v>0.295</v>
       </c>
       <c r="W63">
-        <v>0.05343900000000001</v>
+        <v>0.06345000000000001</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y63">
-        <v>2.010793886835192</v>
+        <v>1.666220210385047</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6627,22 +6627,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1114226048530313</v>
+        <v>0.1114016934782713</v>
       </c>
       <c r="C64">
-        <v>683.17662815475</v>
+        <v>666.3466728449696</v>
       </c>
       <c r="D64">
-        <v>1728.69862815475</v>
+        <v>1729.24967284497</v>
       </c>
       <c r="E64">
-        <v>1036.422</v>
+        <v>1053.803</v>
       </c>
       <c r="F64">
-        <v>1077.622</v>
+        <v>1095.003</v>
       </c>
       <c r="G64">
         <v>32.1</v>
@@ -6663,28 +6663,28 @@
         <v>161.6</v>
       </c>
       <c r="M64">
-        <v>96.98598</v>
+        <v>98.55027000000001</v>
       </c>
       <c r="N64">
-        <v>64.61402</v>
+        <v>63.04972999999998</v>
       </c>
       <c r="O64">
-        <v>19.0611359</v>
+        <v>18.59967034999999</v>
       </c>
       <c r="P64">
-        <v>45.5528841</v>
+        <v>44.45005964999999</v>
       </c>
       <c r="Q64">
-        <v>137.7528841</v>
+        <v>136.65005965</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1896936969816614</v>
+        <v>0.1930491715628953</v>
       </c>
       <c r="T64">
-        <v>2.225989728626806</v>
+        <v>2.277897853229699</v>
       </c>
       <c r="U64">
         <v>0.09</v>
@@ -6701,7 +6701,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>1.666220210385047</v>
+        <v>1.639772270537665</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1114016934782713</v>
+        <v>0.1113807821035112</v>
       </c>
       <c r="C65">
-        <v>666.3466728449696</v>
+        <v>649.5170689522229</v>
       </c>
       <c r="D65">
-        <v>1729.24967284497</v>
+        <v>1729.801068952223</v>
       </c>
       <c r="E65">
-        <v>1053.803</v>
+        <v>1071.184</v>
       </c>
       <c r="F65">
-        <v>1095.003</v>
+        <v>1112.384</v>
       </c>
       <c r="G65">
         <v>32.1</v>
@@ -6745,28 +6745,28 @@
         <v>161.6</v>
       </c>
       <c r="M65">
-        <v>98.55027000000001</v>
+        <v>100.11456</v>
       </c>
       <c r="N65">
-        <v>63.04972999999998</v>
+        <v>61.48544</v>
       </c>
       <c r="O65">
-        <v>18.59967034999999</v>
+        <v>18.1382048</v>
       </c>
       <c r="P65">
-        <v>44.45005964999999</v>
+        <v>43.3472352</v>
       </c>
       <c r="Q65">
-        <v>136.65005965</v>
+        <v>135.5472352</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1930491715628953</v>
+        <v>0.1965910613986423</v>
       </c>
       <c r="T65">
-        <v>2.277897853229699</v>
+        <v>2.332689762532754</v>
       </c>
       <c r="U65">
         <v>0.09</v>
@@ -6783,7 +6783,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>1.639772270537665</v>
+        <v>1.614150828810515</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6791,22 +6791,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1113807821035112</v>
+        <v>0.1113598707287512</v>
       </c>
       <c r="C66">
-        <v>649.5170689522229</v>
+        <v>632.6878168127837</v>
       </c>
       <c r="D66">
-        <v>1729.801068952223</v>
+        <v>1730.352816812784</v>
       </c>
       <c r="E66">
-        <v>1071.184</v>
+        <v>1088.565</v>
       </c>
       <c r="F66">
-        <v>1112.384</v>
+        <v>1129.765</v>
       </c>
       <c r="G66">
         <v>32.1</v>
@@ -6827,28 +6827,28 @@
         <v>161.6</v>
       </c>
       <c r="M66">
-        <v>100.11456</v>
+        <v>101.67885</v>
       </c>
       <c r="N66">
-        <v>61.48544</v>
+        <v>59.92114999999998</v>
       </c>
       <c r="O66">
-        <v>18.1382048</v>
+        <v>17.67673924999999</v>
       </c>
       <c r="P66">
-        <v>43.3472352</v>
+        <v>42.24441074999999</v>
       </c>
       <c r="Q66">
-        <v>135.5472352</v>
+        <v>134.44441075</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1965910613986423</v>
+        <v>0.2003353449392891</v>
       </c>
       <c r="T66">
-        <v>2.332689762532754</v>
+        <v>2.390612638081697</v>
       </c>
       <c r="U66">
         <v>0.09</v>
@@ -6865,7 +6865,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>1.614150828810515</v>
+        <v>1.589317739136507</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6873,22 +6873,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1113598707287512</v>
+        <v>0.1113389593539911</v>
       </c>
       <c r="C67">
-        <v>632.6878168127837</v>
+        <v>615.8589167633493</v>
       </c>
       <c r="D67">
-        <v>1730.352816812784</v>
+        <v>1730.90491676335</v>
       </c>
       <c r="E67">
-        <v>1088.565</v>
+        <v>1105.946</v>
       </c>
       <c r="F67">
-        <v>1129.765</v>
+        <v>1147.146</v>
       </c>
       <c r="G67">
         <v>32.1</v>
@@ -6909,28 +6909,28 @@
         <v>161.6</v>
       </c>
       <c r="M67">
-        <v>101.67885</v>
+        <v>103.24314</v>
       </c>
       <c r="N67">
-        <v>59.92114999999998</v>
+        <v>58.35685999999998</v>
       </c>
       <c r="O67">
-        <v>17.67673924999999</v>
+        <v>17.21527369999999</v>
       </c>
       <c r="P67">
-        <v>42.24441074999999</v>
+        <v>41.14158629999999</v>
       </c>
       <c r="Q67">
-        <v>134.44441075</v>
+        <v>133.3415863</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2003353449392891</v>
+        <v>0.2042998804529151</v>
       </c>
       <c r="T67">
-        <v>2.390612638081697</v>
+        <v>2.451942741604107</v>
       </c>
       <c r="U67">
         <v>0.09</v>
@@ -6947,7 +6947,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>1.589317739136507</v>
+        <v>1.565237167331408</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6955,22 +6955,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1113389593539911</v>
+        <v>0.111318047979231</v>
       </c>
       <c r="C68">
-        <v>615.8589167633493</v>
+        <v>599.0303691410509</v>
       </c>
       <c r="D68">
-        <v>1730.90491676335</v>
+        <v>1731.457369141051</v>
       </c>
       <c r="E68">
-        <v>1105.946</v>
+        <v>1123.327</v>
       </c>
       <c r="F68">
-        <v>1147.146</v>
+        <v>1164.527</v>
       </c>
       <c r="G68">
         <v>32.1</v>
@@ -6991,28 +6991,28 @@
         <v>161.6</v>
       </c>
       <c r="M68">
-        <v>103.24314</v>
+        <v>104.80743</v>
       </c>
       <c r="N68">
-        <v>58.35685999999998</v>
+        <v>56.79256999999997</v>
       </c>
       <c r="O68">
-        <v>17.21527369999999</v>
+        <v>16.75380814999999</v>
       </c>
       <c r="P68">
-        <v>41.14158629999999</v>
+        <v>40.03876184999998</v>
       </c>
       <c r="Q68">
-        <v>133.3415863</v>
+        <v>132.23876185</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2042998804529151</v>
+        <v>0.2085046908461547</v>
       </c>
       <c r="T68">
-        <v>2.451942741604107</v>
+        <v>2.516989821097572</v>
       </c>
       <c r="U68">
         <v>0.09</v>
@@ -7029,7 +7029,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>1.565237167331408</v>
+        <v>1.541875418565267</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7037,22 +7037,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.111318047979231</v>
+        <v>0.111297136604471</v>
       </c>
       <c r="C69">
-        <v>599.0303691410509</v>
+        <v>582.202174283447</v>
       </c>
       <c r="D69">
-        <v>1731.457369141051</v>
+        <v>1732.010174283447</v>
       </c>
       <c r="E69">
-        <v>1123.327</v>
+        <v>1140.708</v>
       </c>
       <c r="F69">
-        <v>1164.527</v>
+        <v>1181.908</v>
       </c>
       <c r="G69">
         <v>32.1</v>
@@ -7073,28 +7073,28 @@
         <v>161.6</v>
       </c>
       <c r="M69">
-        <v>104.80743</v>
+        <v>106.37172</v>
       </c>
       <c r="N69">
-        <v>56.79256999999997</v>
+        <v>55.22827999999998</v>
       </c>
       <c r="O69">
-        <v>16.75380814999999</v>
+        <v>16.29234259999999</v>
       </c>
       <c r="P69">
-        <v>40.03876184999998</v>
+        <v>38.93593739999999</v>
       </c>
       <c r="Q69">
-        <v>132.23876185</v>
+        <v>131.1359374</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2085046908461547</v>
+        <v>0.2129723018889719</v>
       </c>
       <c r="T69">
-        <v>2.516989821097572</v>
+        <v>2.586102343059379</v>
       </c>
       <c r="U69">
         <v>0.09</v>
@@ -7111,7 +7111,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>1.541875418565267</v>
+        <v>1.519200780056955</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7119,22 +7119,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.111297136604471</v>
+        <v>0.1424785028772895</v>
       </c>
       <c r="C70">
-        <v>582.202174283447</v>
+        <v>6.202225651932167</v>
       </c>
       <c r="D70">
-        <v>1732.010174283447</v>
+        <v>1173.391225651932</v>
       </c>
       <c r="E70">
-        <v>1140.708</v>
+        <v>1158.089</v>
       </c>
       <c r="F70">
-        <v>1181.908</v>
+        <v>1199.289</v>
       </c>
       <c r="G70">
         <v>32.1</v>
@@ -7155,45 +7155,45 @@
         <v>161.6</v>
       </c>
       <c r="M70">
-        <v>106.37172</v>
+        <v>176.0556252</v>
       </c>
       <c r="N70">
-        <v>55.22827999999998</v>
+        <v>-14.45562520000004</v>
       </c>
       <c r="O70">
-        <v>16.29234259999999</v>
+        <v>-4.264409434000012</v>
       </c>
       <c r="P70">
-        <v>38.93593739999999</v>
+        <v>-10.19121576600003</v>
       </c>
       <c r="Q70">
-        <v>131.1359374</v>
+        <v>82.00878423399999</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2129723018889719</v>
+        <v>0.2213359798723798</v>
       </c>
       <c r="T70">
-        <v>2.586102343059379</v>
+        <v>2.715485781494357</v>
       </c>
       <c r="U70">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V70">
-        <v>0.295</v>
+        <v>0.2707780563435243</v>
       </c>
       <c r="W70">
-        <v>0.06345000000000001</v>
+        <v>0.1070497813287706</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y70">
-        <v>1.519200780056955</v>
+        <v>0.9178917164187262</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7201,22 +7201,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1424785028772895</v>
+        <v>0.1434885028772895</v>
       </c>
       <c r="C71">
-        <v>6.202225651932167</v>
+        <v>-23.31044903856014</v>
       </c>
       <c r="D71">
-        <v>1173.391225651932</v>
+        <v>1161.25955096144</v>
       </c>
       <c r="E71">
-        <v>1158.089</v>
+        <v>1175.47</v>
       </c>
       <c r="F71">
-        <v>1199.289</v>
+        <v>1216.67</v>
       </c>
       <c r="G71">
         <v>32.1</v>
@@ -7237,37 +7237,37 @@
         <v>161.6</v>
       </c>
       <c r="M71">
-        <v>176.0556252</v>
+        <v>178.6071560000001</v>
       </c>
       <c r="N71">
-        <v>-14.45562520000004</v>
+        <v>-17.00715600000007</v>
       </c>
       <c r="O71">
-        <v>-4.264409434000012</v>
+        <v>-5.017111020000019</v>
       </c>
       <c r="P71">
-        <v>-10.19121576600003</v>
+        <v>-11.99004498000005</v>
       </c>
       <c r="Q71">
-        <v>82.00878423399999</v>
+        <v>80.20995501999997</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2213359798723798</v>
+        <v>0.2271871792014591</v>
       </c>
       <c r="T71">
-        <v>2.715485781494357</v>
+        <v>2.806001974210836</v>
       </c>
       <c r="U71">
         <v>0.1468</v>
       </c>
       <c r="V71">
-        <v>0.2707780563435243</v>
+        <v>0.2669097983957596</v>
       </c>
       <c r="W71">
-        <v>0.1070497813287706</v>
+        <v>0.1076176415955025</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7275,7 +7275,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.9178917164187262</v>
+        <v>0.9047789776127444</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7283,22 +7283,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1434885028772895</v>
+        <v>0.1444985028772895</v>
       </c>
       <c r="C72">
-        <v>-23.31044903856014</v>
+        <v>-52.57483239574481</v>
       </c>
       <c r="D72">
-        <v>1161.25955096144</v>
+        <v>1149.376167604255</v>
       </c>
       <c r="E72">
-        <v>1175.47</v>
+        <v>1192.851</v>
       </c>
       <c r="F72">
-        <v>1216.67</v>
+        <v>1234.051</v>
       </c>
       <c r="G72">
         <v>32.1</v>
@@ -7319,37 +7319,37 @@
         <v>161.6</v>
       </c>
       <c r="M72">
-        <v>178.6071560000001</v>
+        <v>181.1586868</v>
       </c>
       <c r="N72">
-        <v>-17.00715600000007</v>
+        <v>-19.55868680000003</v>
       </c>
       <c r="O72">
-        <v>-5.017111020000019</v>
+        <v>-5.769812606000009</v>
       </c>
       <c r="P72">
-        <v>-11.99004498000005</v>
+        <v>-13.78887419400002</v>
       </c>
       <c r="Q72">
-        <v>80.20995501999997</v>
+        <v>78.411125806</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2271871792014591</v>
+        <v>0.2334419095187508</v>
       </c>
       <c r="T72">
-        <v>2.806001974210836</v>
+        <v>2.902760662976727</v>
       </c>
       <c r="U72">
         <v>0.1468</v>
       </c>
       <c r="V72">
-        <v>0.2669097983957596</v>
+        <v>0.2631505054606081</v>
       </c>
       <c r="W72">
-        <v>0.1076176415955025</v>
+        <v>0.1081695057983827</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7357,7 +7357,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.9047789776127444</v>
+        <v>0.8920356117308749</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7365,22 +7365,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1444985028772895</v>
+        <v>0.1455085028772895</v>
       </c>
       <c r="C73">
-        <v>-52.57483239574458</v>
+        <v>-81.59846964112558</v>
       </c>
       <c r="D73">
-        <v>1149.376167604255</v>
+        <v>1137.733530358875</v>
       </c>
       <c r="E73">
-        <v>1192.851</v>
+        <v>1210.232</v>
       </c>
       <c r="F73">
-        <v>1234.051</v>
+        <v>1251.432</v>
       </c>
       <c r="G73">
         <v>32.1</v>
@@ -7401,37 +7401,37 @@
         <v>161.6</v>
       </c>
       <c r="M73">
-        <v>181.1586868</v>
+        <v>183.7102176</v>
       </c>
       <c r="N73">
-        <v>-19.5586868</v>
+        <v>-22.11021760000003</v>
       </c>
       <c r="O73">
-        <v>-5.769812606000001</v>
+        <v>-6.522514192000008</v>
       </c>
       <c r="P73">
-        <v>-13.788874194</v>
+        <v>-15.58770340800002</v>
       </c>
       <c r="Q73">
-        <v>78.41112580600002</v>
+        <v>76.61229659199999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2334419095187507</v>
+        <v>0.2401434062872776</v>
       </c>
       <c r="T73">
-        <v>2.902760662976726</v>
+        <v>3.006430686654467</v>
       </c>
       <c r="U73">
         <v>0.1468</v>
       </c>
       <c r="V73">
-        <v>0.2631505054606081</v>
+        <v>0.2594956373292108</v>
       </c>
       <c r="W73">
-        <v>0.1081695057983827</v>
+        <v>0.1087060404400719</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7439,7 +7439,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.892035611730875</v>
+        <v>0.8796462282346128</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7447,22 +7447,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1455085028772895</v>
+        <v>0.1465185028772895</v>
       </c>
       <c r="C74">
-        <v>-81.59846964112558</v>
+        <v>-110.3886033438225</v>
       </c>
       <c r="D74">
-        <v>1137.733530358875</v>
+        <v>1126.324396656178</v>
       </c>
       <c r="E74">
-        <v>1210.232</v>
+        <v>1227.613</v>
       </c>
       <c r="F74">
-        <v>1251.432</v>
+        <v>1268.813</v>
       </c>
       <c r="G74">
         <v>32.1</v>
@@ -7483,37 +7483,37 @@
         <v>161.6</v>
       </c>
       <c r="M74">
-        <v>183.7102176</v>
+        <v>186.2617484</v>
       </c>
       <c r="N74">
-        <v>-22.11021760000003</v>
+        <v>-24.66174840000005</v>
       </c>
       <c r="O74">
-        <v>-6.522514192000008</v>
+        <v>-7.275215778000015</v>
       </c>
       <c r="P74">
-        <v>-15.58770340800002</v>
+        <v>-17.38653262200004</v>
       </c>
       <c r="Q74">
-        <v>76.61229659199999</v>
+        <v>74.81346737799998</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2401434062872776</v>
+        <v>0.2473413102238434</v>
       </c>
       <c r="T74">
-        <v>3.006430686654467</v>
+        <v>3.117779971345373</v>
       </c>
       <c r="U74">
         <v>0.1468</v>
       </c>
       <c r="V74">
-        <v>0.2594956373292108</v>
+        <v>0.2559409025712763</v>
       </c>
       <c r="W74">
-        <v>0.1087060404400719</v>
+        <v>0.1092278755025366</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7521,7 +7521,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.8796462282346128</v>
+        <v>0.8675962799026317</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7529,22 +7529,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1465185028772895</v>
+        <v>0.1475285028772895</v>
       </c>
       <c r="C75">
-        <v>-110.3886033438225</v>
+        <v>-138.9521884448238</v>
       </c>
       <c r="D75">
-        <v>1126.324396656178</v>
+        <v>1115.141811555176</v>
       </c>
       <c r="E75">
-        <v>1227.613</v>
+        <v>1244.994</v>
       </c>
       <c r="F75">
-        <v>1268.813</v>
+        <v>1286.194</v>
       </c>
       <c r="G75">
         <v>32.1</v>
@@ -7565,37 +7565,37 @@
         <v>161.6</v>
       </c>
       <c r="M75">
-        <v>186.2617484</v>
+        <v>188.8132792</v>
       </c>
       <c r="N75">
-        <v>-24.66174840000005</v>
+        <v>-27.21327920000004</v>
       </c>
       <c r="O75">
-        <v>-7.275215778000015</v>
+        <v>-8.027917364000013</v>
       </c>
       <c r="P75">
-        <v>-17.38653262200004</v>
+        <v>-19.18536183600003</v>
       </c>
       <c r="Q75">
-        <v>74.81346737799998</v>
+        <v>73.01463816399999</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2473413102238434</v>
+        <v>0.2550928990786065</v>
       </c>
       <c r="T75">
-        <v>3.117779971345373</v>
+        <v>3.237694585627886</v>
       </c>
       <c r="U75">
         <v>0.1468</v>
       </c>
       <c r="V75">
-        <v>0.2559409025712763</v>
+        <v>0.2524822417257185</v>
       </c>
       <c r="W75">
-        <v>0.1092278755025366</v>
+        <v>0.1097356069146645</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7603,7 +7603,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.8675962799026317</v>
+        <v>0.8558720058498934</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7611,22 +7611,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1475285028772895</v>
+        <v>0.1485385028772895</v>
       </c>
       <c r="C76">
-        <v>-138.9521884448238</v>
+        <v>-167.2959063950352</v>
       </c>
       <c r="D76">
-        <v>1115.141811555176</v>
+        <v>1104.179093604965</v>
       </c>
       <c r="E76">
-        <v>1244.994</v>
+        <v>1262.375</v>
       </c>
       <c r="F76">
-        <v>1286.194</v>
+        <v>1303.575</v>
       </c>
       <c r="G76">
         <v>32.1</v>
@@ -7647,37 +7647,37 @@
         <v>161.6</v>
       </c>
       <c r="M76">
-        <v>188.8132792</v>
+        <v>191.36481</v>
       </c>
       <c r="N76">
-        <v>-27.21327920000004</v>
+        <v>-29.76481000000004</v>
       </c>
       <c r="O76">
-        <v>-8.027917364000013</v>
+        <v>-8.780618950000012</v>
       </c>
       <c r="P76">
-        <v>-19.18536183600003</v>
+        <v>-20.98419105000003</v>
       </c>
       <c r="Q76">
-        <v>73.01463816399999</v>
+        <v>71.21580895</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2550928990786065</v>
+        <v>0.2634646150417508</v>
       </c>
       <c r="T76">
-        <v>3.237694585627886</v>
+        <v>3.367202369053003</v>
       </c>
       <c r="U76">
         <v>0.1468</v>
       </c>
       <c r="V76">
-        <v>0.2524822417257185</v>
+        <v>0.2491158118360423</v>
       </c>
       <c r="W76">
-        <v>0.1097356069146645</v>
+        <v>0.110229798822469</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7685,7 +7685,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.8558720058498934</v>
+        <v>0.8444603791052282</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7693,22 +7693,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1485385028772895</v>
+        <v>0.1495485028772895</v>
       </c>
       <c r="C77">
-        <v>-167.2959063950352</v>
+        <v>-195.4261784675211</v>
       </c>
       <c r="D77">
-        <v>1104.179093604965</v>
+        <v>1093.429821532479</v>
       </c>
       <c r="E77">
-        <v>1262.375</v>
+        <v>1279.756</v>
       </c>
       <c r="F77">
-        <v>1303.575</v>
+        <v>1320.956</v>
       </c>
       <c r="G77">
         <v>32.1</v>
@@ -7729,37 +7729,37 @@
         <v>161.6</v>
       </c>
       <c r="M77">
-        <v>191.36481</v>
+        <v>193.9163408</v>
       </c>
       <c r="N77">
-        <v>-29.76481000000004</v>
+        <v>-32.31634080000003</v>
       </c>
       <c r="O77">
-        <v>-8.780618950000012</v>
+        <v>-9.53332053600001</v>
       </c>
       <c r="P77">
-        <v>-20.98419105000003</v>
+        <v>-22.78302026400002</v>
       </c>
       <c r="Q77">
-        <v>71.21580895</v>
+        <v>69.416979736</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2634646150417508</v>
+        <v>0.2725339740018238</v>
       </c>
       <c r="T77">
-        <v>3.367202369053003</v>
+        <v>3.507502467763544</v>
       </c>
       <c r="U77">
         <v>0.1468</v>
       </c>
       <c r="V77">
-        <v>0.2491158118360423</v>
+        <v>0.2458379722066207</v>
       </c>
       <c r="W77">
-        <v>0.110229798822469</v>
+        <v>0.1107109856800681</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.8444603791052282</v>
+        <v>0.8333490583275278</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7775,22 +7775,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1495485028772895</v>
+        <v>0.1505585028772894</v>
       </c>
       <c r="C78">
-        <v>-195.4261784675211</v>
+        <v>-223.3491782996623</v>
       </c>
       <c r="D78">
-        <v>1093.429821532479</v>
+        <v>1082.887821700338</v>
       </c>
       <c r="E78">
-        <v>1279.756</v>
+        <v>1297.137</v>
       </c>
       <c r="F78">
-        <v>1320.956</v>
+        <v>1338.337</v>
       </c>
       <c r="G78">
         <v>32.1</v>
@@ -7811,37 +7811,37 @@
         <v>161.6</v>
       </c>
       <c r="M78">
-        <v>193.9163408</v>
+        <v>196.4678716000001</v>
       </c>
       <c r="N78">
-        <v>-32.31634080000003</v>
+        <v>-34.86787160000006</v>
       </c>
       <c r="O78">
-        <v>-9.53332053600001</v>
+        <v>-10.28602212200002</v>
       </c>
       <c r="P78">
-        <v>-22.78302026400002</v>
+        <v>-24.58184947800004</v>
       </c>
       <c r="Q78">
-        <v>69.416979736</v>
+        <v>67.61815052199998</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2725339740018238</v>
+        <v>0.2823919728714683</v>
       </c>
       <c r="T78">
-        <v>3.507502467763544</v>
+        <v>3.660002575057612</v>
       </c>
       <c r="U78">
         <v>0.1468</v>
       </c>
       <c r="V78">
-        <v>0.2458379722066207</v>
+        <v>0.2426452712688723</v>
       </c>
       <c r="W78">
-        <v>0.1107109856800681</v>
+        <v>0.1111796741777295</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7849,7 +7849,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.8333490583275278</v>
+        <v>0.8225263432843131</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7857,22 +7857,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1505585028772894</v>
+        <v>0.1515685028772895</v>
       </c>
       <c r="C79">
-        <v>-223.3491782996623</v>
+        <v>-251.0708437167218</v>
       </c>
       <c r="D79">
-        <v>1082.887821700338</v>
+        <v>1072.547156283278</v>
       </c>
       <c r="E79">
-        <v>1297.137</v>
+        <v>1314.518</v>
       </c>
       <c r="F79">
-        <v>1338.337</v>
+        <v>1355.718</v>
       </c>
       <c r="G79">
         <v>32.1</v>
@@ -7893,37 +7893,37 @@
         <v>161.6</v>
       </c>
       <c r="M79">
-        <v>196.4678716000001</v>
+        <v>199.0194024</v>
       </c>
       <c r="N79">
-        <v>-34.86787160000006</v>
+        <v>-37.41940240000002</v>
       </c>
       <c r="O79">
-        <v>-10.28602212200002</v>
+        <v>-11.03872370800001</v>
       </c>
       <c r="P79">
-        <v>-24.58184947800004</v>
+        <v>-26.38067869200002</v>
       </c>
       <c r="Q79">
-        <v>67.61815052199998</v>
+        <v>65.819321308</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2823919728714683</v>
+        <v>0.2931461534565351</v>
       </c>
       <c r="T79">
-        <v>3.660002575057612</v>
+        <v>3.826366328469321</v>
       </c>
       <c r="U79">
         <v>0.1468</v>
       </c>
       <c r="V79">
-        <v>0.2426452712688723</v>
+        <v>0.239534434457733</v>
       </c>
       <c r="W79">
-        <v>0.1111796741777295</v>
+        <v>0.1116363450216048</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.8225263432843131</v>
+        <v>0.8119811337550272</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7939,22 +7939,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1515685028772895</v>
+        <v>0.1525785028772895</v>
       </c>
       <c r="C80">
-        <v>-251.0708437167218</v>
+        <v>-278.5968878843762</v>
       </c>
       <c r="D80">
-        <v>1072.547156283278</v>
+        <v>1062.402112115624</v>
       </c>
       <c r="E80">
-        <v>1314.518</v>
+        <v>1331.899</v>
       </c>
       <c r="F80">
-        <v>1355.718</v>
+        <v>1373.099</v>
       </c>
       <c r="G80">
         <v>32.1</v>
@@ -7975,37 +7975,37 @@
         <v>161.6</v>
       </c>
       <c r="M80">
-        <v>199.0194024</v>
+        <v>201.5709332</v>
       </c>
       <c r="N80">
-        <v>-37.41940240000002</v>
+        <v>-39.97093320000005</v>
       </c>
       <c r="O80">
-        <v>-11.03872370800001</v>
+        <v>-11.79142529400001</v>
       </c>
       <c r="P80">
-        <v>-26.38067869200002</v>
+        <v>-28.17950790600003</v>
       </c>
       <c r="Q80">
-        <v>65.819321308</v>
+        <v>64.02049209399999</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2931461534565351</v>
+        <v>0.3049245417163701</v>
       </c>
       <c r="T80">
-        <v>3.826366328469321</v>
+        <v>4.008574248872622</v>
       </c>
       <c r="U80">
         <v>0.1468</v>
       </c>
       <c r="V80">
-        <v>0.239534434457733</v>
+        <v>0.2365023530089009</v>
       </c>
       <c r="W80">
-        <v>0.1116363450216048</v>
+        <v>0.1120814545782934</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8013,7 +8013,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.8119811337550272</v>
+        <v>0.8017028915555964</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8021,22 +8021,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1525785028772895</v>
+        <v>0.2001508516905202</v>
       </c>
       <c r="C81">
-        <v>-278.5968878843762</v>
+        <v>-623.419967431914</v>
       </c>
       <c r="D81">
-        <v>1062.402112115624</v>
+        <v>734.9600325680863</v>
       </c>
       <c r="E81">
-        <v>1331.899</v>
+        <v>1349.28</v>
       </c>
       <c r="F81">
-        <v>1373.099</v>
+        <v>1390.48</v>
       </c>
       <c r="G81">
         <v>32.1</v>
@@ -8057,45 +8057,45 @@
         <v>161.6</v>
       </c>
       <c r="M81">
-        <v>201.5709332</v>
+        <v>279.2083840000001</v>
       </c>
       <c r="N81">
-        <v>-39.97093320000005</v>
+        <v>-117.6083840000001</v>
       </c>
       <c r="O81">
-        <v>-11.79142529400001</v>
+        <v>-34.69447328000003</v>
       </c>
       <c r="P81">
-        <v>-28.17950790600003</v>
+        <v>-82.91391072000006</v>
       </c>
       <c r="Q81">
-        <v>64.02049209399999</v>
+        <v>9.286089279999956</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3049245417163701</v>
+        <v>0.3346925128683421</v>
       </c>
       <c r="T81">
-        <v>4.008574248872622</v>
+        <v>4.469075295244332</v>
       </c>
       <c r="U81">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.2365023530089009</v>
+        <v>0.1707398585853352</v>
       </c>
       <c r="W81">
-        <v>0.1120814545782934</v>
+        <v>0.1665154363960647</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y81">
-        <v>0.8017028915555964</v>
+        <v>0.5787791816452043</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8103,22 +8103,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2001508516905202</v>
+        <v>0.2017008516905202</v>
       </c>
       <c r="C82">
-        <v>-623.419967431914</v>
+        <v>-648.1080991000714</v>
       </c>
       <c r="D82">
-        <v>734.9600325680863</v>
+        <v>727.6529008999287</v>
       </c>
       <c r="E82">
-        <v>1349.28</v>
+        <v>1366.661</v>
       </c>
       <c r="F82">
-        <v>1390.48</v>
+        <v>1407.861</v>
       </c>
       <c r="G82">
         <v>32.1</v>
@@ -8139,37 +8139,37 @@
         <v>161.6</v>
       </c>
       <c r="M82">
-        <v>279.2083840000001</v>
+        <v>282.6984888</v>
       </c>
       <c r="N82">
-        <v>-117.6083840000001</v>
+        <v>-121.0984888</v>
       </c>
       <c r="O82">
-        <v>-34.69447328000003</v>
+        <v>-35.724054196</v>
       </c>
       <c r="P82">
-        <v>-82.91391072000006</v>
+        <v>-85.37443460400002</v>
       </c>
       <c r="Q82">
-        <v>9.286089279999956</v>
+        <v>6.825565396000002</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3346925128683421</v>
+        <v>0.349897381966676</v>
       </c>
       <c r="T82">
-        <v>4.469075295244332</v>
+        <v>4.704289784467719</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.1707398585853352</v>
+        <v>0.1686319590966275</v>
       </c>
       <c r="W82">
-        <v>0.1665154363960647</v>
+        <v>0.1669387026133972</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8177,7 +8177,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.5787791816452043</v>
+        <v>0.5716337596495846</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8185,22 +8185,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2017008516905202</v>
+        <v>0.2032508516905202</v>
       </c>
       <c r="C83">
-        <v>-648.1080991000714</v>
+        <v>-672.65236296486</v>
       </c>
       <c r="D83">
-        <v>727.6529008999287</v>
+        <v>720.4896370351402</v>
       </c>
       <c r="E83">
-        <v>1366.661</v>
+        <v>1384.042</v>
       </c>
       <c r="F83">
-        <v>1407.861</v>
+        <v>1425.242</v>
       </c>
       <c r="G83">
         <v>32.1</v>
@@ -8221,37 +8221,37 @@
         <v>161.6</v>
       </c>
       <c r="M83">
-        <v>282.6984888</v>
+        <v>286.1885936</v>
       </c>
       <c r="N83">
-        <v>-121.0984888</v>
+        <v>-124.5885936000001</v>
       </c>
       <c r="O83">
-        <v>-35.724054196</v>
+        <v>-36.75363511200001</v>
       </c>
       <c r="P83">
-        <v>-85.37443460400002</v>
+        <v>-87.83495848800004</v>
       </c>
       <c r="Q83">
-        <v>6.825565396000002</v>
+        <v>4.365041511999976</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.349897381966676</v>
+        <v>0.3667916809648247</v>
       </c>
       <c r="T83">
-        <v>4.704289784467719</v>
+        <v>4.965639216938148</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.1686319590966275</v>
+        <v>0.166575471790571</v>
       </c>
       <c r="W83">
-        <v>0.1669387026133972</v>
+        <v>0.1673516452644533</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.5716337596495846</v>
+        <v>0.5646626162392238</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8267,22 +8267,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2032508516905202</v>
+        <v>0.2048008516905202</v>
       </c>
       <c r="C84">
-        <v>-672.65236296486</v>
+        <v>-697.0569664583694</v>
       </c>
       <c r="D84">
-        <v>720.4896370351402</v>
+        <v>713.4660335416308</v>
       </c>
       <c r="E84">
-        <v>1384.042</v>
+        <v>1401.423</v>
       </c>
       <c r="F84">
-        <v>1425.242</v>
+        <v>1442.623</v>
       </c>
       <c r="G84">
         <v>32.1</v>
@@ -8303,37 +8303,37 @@
         <v>161.6</v>
       </c>
       <c r="M84">
-        <v>286.1885936</v>
+        <v>289.6786984000001</v>
       </c>
       <c r="N84">
-        <v>-124.5885936000001</v>
+        <v>-128.0786984000001</v>
       </c>
       <c r="O84">
-        <v>-36.75363511200001</v>
+        <v>-37.78321602800003</v>
       </c>
       <c r="P84">
-        <v>-87.83495848800004</v>
+        <v>-90.29548237200007</v>
       </c>
       <c r="Q84">
-        <v>4.365041511999976</v>
+        <v>1.904517627999951</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3667916809648247</v>
+        <v>0.3856735445509908</v>
       </c>
       <c r="T84">
-        <v>4.965639216938148</v>
+        <v>5.257735641463921</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.166575471790571</v>
+        <v>0.1645685383955039</v>
       </c>
       <c r="W84">
-        <v>0.1673516452644533</v>
+        <v>0.1677546374901828</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8341,7 +8341,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.5646626162392238</v>
+        <v>0.5578594521881487</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8349,22 +8349,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2048008516905202</v>
+        <v>0.2063508516905202</v>
       </c>
       <c r="C85">
-        <v>-697.0569664583694</v>
+        <v>-721.3259545340804</v>
       </c>
       <c r="D85">
-        <v>713.4660335416308</v>
+        <v>706.5780454659199</v>
       </c>
       <c r="E85">
-        <v>1401.423</v>
+        <v>1418.804</v>
       </c>
       <c r="F85">
-        <v>1442.623</v>
+        <v>1460.004</v>
       </c>
       <c r="G85">
         <v>32.1</v>
@@ -8385,37 +8385,37 @@
         <v>161.6</v>
       </c>
       <c r="M85">
-        <v>289.6786984000001</v>
+        <v>293.1688032000001</v>
       </c>
       <c r="N85">
-        <v>-128.0786984000001</v>
+        <v>-131.5688032000001</v>
       </c>
       <c r="O85">
-        <v>-37.78321602800003</v>
+        <v>-38.81279694400002</v>
       </c>
       <c r="P85">
-        <v>-90.29548237200007</v>
+        <v>-92.75600625600006</v>
       </c>
       <c r="Q85">
-        <v>1.904517627999951</v>
+        <v>-0.5560062560000461</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3856735445509908</v>
+        <v>0.4069156410854279</v>
       </c>
       <c r="T85">
-        <v>5.257735641463921</v>
+        <v>5.586344119055418</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.1645685383955039</v>
+        <v>0.1626093891288907</v>
       </c>
       <c r="W85">
-        <v>0.1677546374901828</v>
+        <v>0.1681480346629187</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8423,7 +8423,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.5578594521881487</v>
+        <v>0.5512182682335279</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8431,22 +8431,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2063508516905201</v>
+        <v>0.2079008516905202</v>
       </c>
       <c r="C86">
-        <v>-721.32595453408</v>
+        <v>-745.4632174349258</v>
       </c>
       <c r="D86">
-        <v>706.5780454659201</v>
+        <v>699.8217825650742</v>
       </c>
       <c r="E86">
-        <v>1418.804</v>
+        <v>1436.185</v>
       </c>
       <c r="F86">
-        <v>1460.004</v>
+        <v>1477.385</v>
       </c>
       <c r="G86">
         <v>32.1</v>
@@ -8467,37 +8467,37 @@
         <v>161.6</v>
       </c>
       <c r="M86">
-        <v>293.1688032</v>
+        <v>296.658908</v>
       </c>
       <c r="N86">
-        <v>-131.5688032</v>
+        <v>-135.058908</v>
       </c>
       <c r="O86">
-        <v>-38.81279694400001</v>
+        <v>-39.84237786</v>
       </c>
       <c r="P86">
-        <v>-92.75600625600001</v>
+        <v>-95.21653014</v>
       </c>
       <c r="Q86">
-        <v>-0.5560062559999892</v>
+        <v>-3.016530139999986</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4069156410854275</v>
+        <v>0.4309900171577894</v>
       </c>
       <c r="T86">
-        <v>5.586344119055413</v>
+        <v>5.958767060325775</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.1626093891288908</v>
+        <v>0.1606963374920803</v>
       </c>
       <c r="W86">
-        <v>0.1681480346629187</v>
+        <v>0.1685321754315903</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8505,7 +8505,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.551218268233528</v>
+        <v>0.5447333474307807</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8513,22 +8513,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2079008516905202</v>
+        <v>0.2094508516905202</v>
       </c>
       <c r="C87">
-        <v>-745.4632174349258</v>
+        <v>-769.4724980199069</v>
       </c>
       <c r="D87">
-        <v>699.8217825650742</v>
+        <v>693.1935019800932</v>
       </c>
       <c r="E87">
-        <v>1436.185</v>
+        <v>1453.566</v>
       </c>
       <c r="F87">
-        <v>1477.385</v>
+        <v>1494.766</v>
       </c>
       <c r="G87">
         <v>32.1</v>
@@ -8549,37 +8549,37 @@
         <v>161.6</v>
       </c>
       <c r="M87">
-        <v>296.658908</v>
+        <v>300.1490128</v>
       </c>
       <c r="N87">
-        <v>-135.058908</v>
+        <v>-138.5490128</v>
       </c>
       <c r="O87">
-        <v>-39.84237786</v>
+        <v>-40.87195877600001</v>
       </c>
       <c r="P87">
-        <v>-95.21653014</v>
+        <v>-97.67705402400003</v>
       </c>
       <c r="Q87">
-        <v>-3.016530139999986</v>
+        <v>-5.477054024000012</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4309900171577894</v>
+        <v>0.4585035898119172</v>
       </c>
       <c r="T87">
-        <v>5.958767060325775</v>
+        <v>6.384393278920474</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.1606963374920803</v>
+        <v>0.1588277754282189</v>
       </c>
       <c r="W87">
-        <v>0.1685321754315903</v>
+        <v>0.1689073826940137</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8587,7 +8587,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.5447333474307807</v>
+        <v>0.538399238739725</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8595,22 +8595,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2094508516905202</v>
+        <v>0.2110008516905201</v>
       </c>
       <c r="C88">
-        <v>-769.4724980199069</v>
+        <v>-793.3573986782517</v>
       </c>
       <c r="D88">
-        <v>693.1935019800932</v>
+        <v>686.6896013217485</v>
       </c>
       <c r="E88">
-        <v>1453.566</v>
+        <v>1470.947</v>
       </c>
       <c r="F88">
-        <v>1494.766</v>
+        <v>1512.147</v>
       </c>
       <c r="G88">
         <v>32.1</v>
@@ -8631,37 +8631,37 @@
         <v>161.6</v>
       </c>
       <c r="M88">
-        <v>300.1490128</v>
+        <v>303.6391176</v>
       </c>
       <c r="N88">
-        <v>-138.5490128</v>
+        <v>-142.0391176</v>
       </c>
       <c r="O88">
-        <v>-40.87195877600001</v>
+        <v>-41.90153969200001</v>
       </c>
       <c r="P88">
-        <v>-97.67705402400003</v>
+        <v>-100.137577908</v>
       </c>
       <c r="Q88">
-        <v>-5.477054024000012</v>
+        <v>-7.937577908000009</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4585035898119172</v>
+        <v>0.4902500197974493</v>
       </c>
       <c r="T88">
-        <v>6.384393278920474</v>
+        <v>6.875500454222047</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.1588277754282189</v>
+        <v>0.1570021688141014</v>
       </c>
       <c r="W88">
-        <v>0.1689073826940137</v>
+        <v>0.1692739645021284</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8669,7 +8669,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.538399238739725</v>
+        <v>0.5322107417427167</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8677,22 +8677,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2110008516905201</v>
+        <v>0.2125508516905201</v>
       </c>
       <c r="C89">
-        <v>-793.3573986782517</v>
+        <v>-817.1213878579658</v>
       </c>
       <c r="D89">
-        <v>686.6896013217485</v>
+        <v>680.3066121420342</v>
       </c>
       <c r="E89">
-        <v>1470.947</v>
+        <v>1488.328</v>
       </c>
       <c r="F89">
-        <v>1512.147</v>
+        <v>1529.528</v>
       </c>
       <c r="G89">
         <v>32.1</v>
@@ -8713,37 +8713,37 @@
         <v>161.6</v>
       </c>
       <c r="M89">
-        <v>303.6391176</v>
+        <v>307.1292224</v>
       </c>
       <c r="N89">
-        <v>-142.0391176</v>
+        <v>-145.5292224</v>
       </c>
       <c r="O89">
-        <v>-41.90153969200001</v>
+        <v>-42.931120608</v>
       </c>
       <c r="P89">
-        <v>-100.137577908</v>
+        <v>-102.598101792</v>
       </c>
       <c r="Q89">
-        <v>-7.937577908000009</v>
+        <v>-10.39810179199999</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4902500197974493</v>
+        <v>0.5272875214472368</v>
       </c>
       <c r="T89">
-        <v>6.875500454222047</v>
+        <v>7.448458825407219</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.1570021688141014</v>
+        <v>0.1552180532593957</v>
       </c>
       <c r="W89">
-        <v>0.1692739645021284</v>
+        <v>0.1696322149055133</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.5322107417427167</v>
+        <v>0.5261628924047312</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8759,22 +8759,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2125508516905201</v>
+        <v>0.2141008516905202</v>
       </c>
       <c r="C90">
-        <v>-817.1213878579658</v>
+        <v>-840.7678062336209</v>
       </c>
       <c r="D90">
-        <v>680.3066121420342</v>
+        <v>674.0411937663791</v>
       </c>
       <c r="E90">
-        <v>1488.328</v>
+        <v>1505.709</v>
       </c>
       <c r="F90">
-        <v>1529.528</v>
+        <v>1546.909</v>
       </c>
       <c r="G90">
         <v>32.1</v>
@@ -8795,37 +8795,37 @@
         <v>161.6</v>
       </c>
       <c r="M90">
-        <v>307.1292224</v>
+        <v>310.6193272</v>
       </c>
       <c r="N90">
-        <v>-145.5292224</v>
+        <v>-149.0193272</v>
       </c>
       <c r="O90">
-        <v>-42.931120608</v>
+        <v>-43.96070152400002</v>
       </c>
       <c r="P90">
-        <v>-102.598101792</v>
+        <v>-105.058625676</v>
       </c>
       <c r="Q90">
-        <v>-10.39810179199999</v>
+        <v>-12.85862567600002</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5272875214472368</v>
+        <v>0.5710591143060766</v>
       </c>
       <c r="T90">
-        <v>7.448458825407219</v>
+        <v>8.125591445898786</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.1552180532593957</v>
+        <v>0.1534740301890654</v>
       </c>
       <c r="W90">
-        <v>0.1696322149055133</v>
+        <v>0.1699824147380357</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8833,7 +8833,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.5261628924047312</v>
+        <v>0.5202509497934421</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8841,22 +8841,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2141008516905202</v>
+        <v>0.2156508516905201</v>
       </c>
       <c r="C91">
-        <v>-840.7678062336209</v>
+        <v>-864.2998725364354</v>
       </c>
       <c r="D91">
-        <v>674.0411937663791</v>
+        <v>667.8901274635648</v>
       </c>
       <c r="E91">
-        <v>1505.709</v>
+        <v>1523.09</v>
       </c>
       <c r="F91">
-        <v>1546.909</v>
+        <v>1564.29</v>
       </c>
       <c r="G91">
         <v>32.1</v>
@@ -8877,37 +8877,37 @@
         <v>161.6</v>
       </c>
       <c r="M91">
-        <v>310.6193272</v>
+        <v>314.109432</v>
       </c>
       <c r="N91">
-        <v>-149.0193272</v>
+        <v>-152.509432</v>
       </c>
       <c r="O91">
-        <v>-43.96070152400002</v>
+        <v>-44.99028244000001</v>
       </c>
       <c r="P91">
-        <v>-105.058625676</v>
+        <v>-107.51914956</v>
       </c>
       <c r="Q91">
-        <v>-12.85862567600002</v>
+        <v>-15.31914956</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5710591143060766</v>
+        <v>0.6235850257366842</v>
       </c>
       <c r="T91">
-        <v>8.125591445898786</v>
+        <v>8.938150590488664</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.1534740301890654</v>
+        <v>0.1517687631869647</v>
       </c>
       <c r="W91">
-        <v>0.1699824147380357</v>
+        <v>0.1703248323520575</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8915,7 +8915,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.5202509497934421</v>
+        <v>0.5144703836846261</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8923,22 +8923,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2156508516905201</v>
+        <v>0.2172008516905202</v>
       </c>
       <c r="C92">
-        <v>-864.2998725364354</v>
+        <v>-887.7206890680227</v>
       </c>
       <c r="D92">
-        <v>667.8901274635648</v>
+        <v>661.8503109319776</v>
       </c>
       <c r="E92">
-        <v>1523.09</v>
+        <v>1540.471</v>
       </c>
       <c r="F92">
-        <v>1564.29</v>
+        <v>1581.671</v>
       </c>
       <c r="G92">
         <v>32.1</v>
@@ -8959,37 +8959,37 @@
         <v>161.6</v>
       </c>
       <c r="M92">
-        <v>314.109432</v>
+        <v>317.5995368000001</v>
       </c>
       <c r="N92">
-        <v>-152.509432</v>
+        <v>-155.9995368000001</v>
       </c>
       <c r="O92">
-        <v>-44.99028244000001</v>
+        <v>-46.01986335600002</v>
       </c>
       <c r="P92">
-        <v>-107.51914956</v>
+        <v>-109.9796734440001</v>
       </c>
       <c r="Q92">
-        <v>-15.31914956</v>
+        <v>-17.77967344400004</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6235850257366842</v>
+        <v>0.6877833619296493</v>
       </c>
       <c r="T92">
-        <v>8.938150590488664</v>
+        <v>9.931278433876296</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.1517687631869647</v>
+        <v>0.1501009745805145</v>
       </c>
       <c r="W92">
-        <v>0.1703248323520575</v>
+        <v>0.1706597243042327</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8997,7 +8997,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.5144703836846261</v>
+        <v>0.508816862984795</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9005,22 +9005,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2172008516905202</v>
+        <v>0.2187508516905202</v>
       </c>
       <c r="C93">
-        <v>-887.7206890680227</v>
+        <v>-911.0332469176494</v>
       </c>
       <c r="D93">
-        <v>661.8503109319776</v>
+        <v>655.9187530823507</v>
       </c>
       <c r="E93">
-        <v>1540.471</v>
+        <v>1557.852</v>
       </c>
       <c r="F93">
-        <v>1581.671</v>
+        <v>1599.052</v>
       </c>
       <c r="G93">
         <v>32.1</v>
@@ -9041,37 +9041,37 @@
         <v>161.6</v>
       </c>
       <c r="M93">
-        <v>317.5995368000001</v>
+        <v>321.0896416</v>
       </c>
       <c r="N93">
-        <v>-155.9995368000001</v>
+        <v>-159.4896416000001</v>
       </c>
       <c r="O93">
-        <v>-46.01986335600002</v>
+        <v>-47.04944427200002</v>
       </c>
       <c r="P93">
-        <v>-109.9796734440001</v>
+        <v>-112.440197328</v>
       </c>
       <c r="Q93">
-        <v>-17.77967344400004</v>
+        <v>-20.24019732800002</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6877833619296493</v>
+        <v>0.7680312821708556</v>
       </c>
       <c r="T93">
-        <v>9.931278433876296</v>
+        <v>11.17268823811084</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.1501009745805145</v>
+        <v>0.1484694422481176</v>
       </c>
       <c r="W93">
-        <v>0.1706597243042327</v>
+        <v>0.170987335996578</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9079,7 +9079,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.508816862984795</v>
+        <v>0.5032862449088733</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9087,22 +9087,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2187508516905202</v>
+        <v>0.2542076000493286</v>
       </c>
       <c r="C94">
-        <v>-911.0332469176494</v>
+        <v>-1040.006847985747</v>
       </c>
       <c r="D94">
-        <v>655.9187530823507</v>
+        <v>544.3261520142535</v>
       </c>
       <c r="E94">
-        <v>1557.852</v>
+        <v>1575.233</v>
       </c>
       <c r="F94">
-        <v>1599.052</v>
+        <v>1616.433</v>
       </c>
       <c r="G94">
         <v>32.1</v>
@@ -9123,45 +9123,45 @@
         <v>161.6</v>
       </c>
       <c r="M94">
-        <v>321.0896416</v>
+        <v>381.1549014000001</v>
       </c>
       <c r="N94">
-        <v>-159.4896416000001</v>
+        <v>-219.5549014000001</v>
       </c>
       <c r="O94">
-        <v>-47.04944427200002</v>
+        <v>-64.76869591300003</v>
       </c>
       <c r="P94">
-        <v>-112.440197328</v>
+        <v>-154.7862054870001</v>
       </c>
       <c r="Q94">
-        <v>-20.24019732800002</v>
+        <v>-62.58620548700006</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.7680312821708556</v>
+        <v>0.8905892990353839</v>
       </c>
       <c r="T94">
-        <v>11.17268823811084</v>
+        <v>13.06862178088498</v>
       </c>
       <c r="U94">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.1484694422481176</v>
+        <v>0.1250725094309386</v>
       </c>
       <c r="W94">
-        <v>0.170987335996578</v>
+        <v>0.2063079022761847</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y94">
-        <v>0.5032862449088733</v>
+        <v>0.42397460824047</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9169,22 +9169,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2542076000493286</v>
+        <v>0.2561076000493286</v>
       </c>
       <c r="C95">
-        <v>-1040.006847985747</v>
+        <v>-1062.305500455674</v>
       </c>
       <c r="D95">
-        <v>544.3261520142535</v>
+        <v>539.408499544326</v>
       </c>
       <c r="E95">
-        <v>1575.233</v>
+        <v>1592.614</v>
       </c>
       <c r="F95">
-        <v>1616.433</v>
+        <v>1633.814</v>
       </c>
       <c r="G95">
         <v>32.1</v>
@@ -9205,37 +9205,37 @@
         <v>161.6</v>
       </c>
       <c r="M95">
-        <v>381.1549014000001</v>
+        <v>385.2533412000001</v>
       </c>
       <c r="N95">
-        <v>-219.5549014000001</v>
+        <v>-223.6533412000001</v>
       </c>
       <c r="O95">
-        <v>-64.76869591300003</v>
+        <v>-65.97773565400003</v>
       </c>
       <c r="P95">
-        <v>-154.7862054870001</v>
+        <v>-157.675605546</v>
       </c>
       <c r="Q95">
-        <v>-62.58620548700006</v>
+        <v>-65.47560554600003</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.8905892990353839</v>
+        <v>1.031387515541281</v>
       </c>
       <c r="T95">
-        <v>13.06862178088498</v>
+        <v>15.24672541103248</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.1250725094309386</v>
+        <v>0.1237419508199712</v>
       </c>
       <c r="W95">
-        <v>0.2063079022761847</v>
+        <v>0.2066216479966508</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9243,7 +9243,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.42397460824047</v>
+        <v>0.419464240067699</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9251,22 +9251,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2561076000493286</v>
+        <v>0.2580076000493286</v>
       </c>
       <c r="C96">
-        <v>-1062.305500455674</v>
+        <v>-1084.516092557446</v>
       </c>
       <c r="D96">
-        <v>539.408499544326</v>
+        <v>534.5789074425541</v>
       </c>
       <c r="E96">
-        <v>1592.614</v>
+        <v>1609.995</v>
       </c>
       <c r="F96">
-        <v>1633.814</v>
+        <v>1651.195</v>
       </c>
       <c r="G96">
         <v>32.1</v>
@@ -9287,37 +9287,37 @@
         <v>161.6</v>
       </c>
       <c r="M96">
-        <v>385.2533412000001</v>
+        <v>389.3517810000001</v>
       </c>
       <c r="N96">
-        <v>-223.6533412000001</v>
+        <v>-227.7517810000001</v>
       </c>
       <c r="O96">
-        <v>-65.97773565400003</v>
+        <v>-67.18677539500003</v>
       </c>
       <c r="P96">
-        <v>-157.675605546</v>
+        <v>-160.5650056050001</v>
       </c>
       <c r="Q96">
-        <v>-65.47560554600003</v>
+        <v>-68.36500560500005</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.031387515541281</v>
+        <v>1.228505018649538</v>
       </c>
       <c r="T96">
-        <v>15.24672541103248</v>
+        <v>18.29607049323899</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.1237419508199712</v>
+        <v>0.1224394039692347</v>
       </c>
       <c r="W96">
-        <v>0.2066216479966508</v>
+        <v>0.2069287885440545</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9325,7 +9325,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.419464240067699</v>
+        <v>0.4150488270143549</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9333,22 +9333,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2580076000493286</v>
+        <v>0.2599076000493286</v>
       </c>
       <c r="C97">
-        <v>-1084.516092557446</v>
+        <v>-1106.640968645483</v>
       </c>
       <c r="D97">
-        <v>534.5789074425541</v>
+        <v>529.8350313545177</v>
       </c>
       <c r="E97">
-        <v>1609.995</v>
+        <v>1627.376</v>
       </c>
       <c r="F97">
-        <v>1651.195</v>
+        <v>1668.576</v>
       </c>
       <c r="G97">
         <v>32.1</v>
@@ -9369,37 +9369,37 @@
         <v>161.6</v>
       </c>
       <c r="M97">
-        <v>389.3517810000001</v>
+        <v>393.4502208000001</v>
       </c>
       <c r="N97">
-        <v>-227.7517810000001</v>
+        <v>-231.8502208000001</v>
       </c>
       <c r="O97">
-        <v>-67.18677539500003</v>
+        <v>-68.39581513600002</v>
       </c>
       <c r="P97">
-        <v>-160.5650056050001</v>
+        <v>-163.454405664</v>
       </c>
       <c r="Q97">
-        <v>-68.36500560500005</v>
+        <v>-71.25440566400002</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.228505018649538</v>
+        <v>1.524181273311924</v>
       </c>
       <c r="T97">
-        <v>18.29607049323899</v>
+        <v>22.87008811654874</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.1224394039692347</v>
+        <v>0.1211639935112218</v>
       </c>
       <c r="W97">
-        <v>0.2069287885440545</v>
+        <v>0.2072295303300539</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9407,7 +9407,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.4150488270143549</v>
+        <v>0.4107254017329554</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9415,22 +9415,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2599076000493286</v>
+        <v>0.2618076000493286</v>
       </c>
       <c r="C98">
-        <v>-1106.640968645482</v>
+        <v>-1128.682390590561</v>
       </c>
       <c r="D98">
-        <v>529.8350313545179</v>
+        <v>525.1746094094394</v>
       </c>
       <c r="E98">
-        <v>1627.376</v>
+        <v>1644.757</v>
       </c>
       <c r="F98">
-        <v>1668.576</v>
+        <v>1685.957</v>
       </c>
       <c r="G98">
         <v>32.1</v>
@@ -9451,37 +9451,37 @@
         <v>161.6</v>
       </c>
       <c r="M98">
-        <v>393.4502208</v>
+        <v>397.5486606000001</v>
       </c>
       <c r="N98">
-        <v>-231.8502208</v>
+        <v>-235.9486606000001</v>
       </c>
       <c r="O98">
-        <v>-68.395815136</v>
+        <v>-69.60485487700002</v>
       </c>
       <c r="P98">
-        <v>-163.454405664</v>
+        <v>-166.3438057230001</v>
       </c>
       <c r="Q98">
-        <v>-71.25440566400002</v>
+        <v>-74.14380572300004</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.52418127331192</v>
+        <v>2.01697503108256</v>
       </c>
       <c r="T98">
-        <v>22.87008811654868</v>
+        <v>30.49345082206491</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.1211639935112218</v>
+        <v>0.1199148801760546</v>
       </c>
       <c r="W98">
-        <v>0.2072295303300539</v>
+        <v>0.2075240712544864</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9489,7 +9489,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.4107254017329554</v>
+        <v>0.406491119240863</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9497,22 +9497,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2618076000493286</v>
+        <v>0.2637076000493286</v>
       </c>
       <c r="C99">
-        <v>-1128.682390590561</v>
+        <v>-1150.642541375811</v>
       </c>
       <c r="D99">
-        <v>525.1746094094394</v>
+        <v>520.595458624189</v>
       </c>
       <c r="E99">
-        <v>1644.757</v>
+        <v>1662.138</v>
       </c>
       <c r="F99">
-        <v>1685.957</v>
+        <v>1703.338</v>
       </c>
       <c r="G99">
         <v>32.1</v>
@@ -9533,37 +9533,37 @@
         <v>161.6</v>
       </c>
       <c r="M99">
-        <v>397.5486606000001</v>
+        <v>401.6471004000001</v>
       </c>
       <c r="N99">
-        <v>-235.9486606000001</v>
+        <v>-240.0471004000001</v>
       </c>
       <c r="O99">
-        <v>-69.60485487700002</v>
+        <v>-70.81389461800002</v>
       </c>
       <c r="P99">
-        <v>-166.3438057230001</v>
+        <v>-169.233205782</v>
       </c>
       <c r="Q99">
-        <v>-74.14380572300004</v>
+        <v>-77.03320578200001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.01697503108256</v>
+        <v>3.002562546623839</v>
       </c>
       <c r="T99">
-        <v>30.49345082206491</v>
+        <v>45.74017623309737</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.1199148801760546</v>
+        <v>0.1186912589497683</v>
       </c>
       <c r="W99">
-        <v>0.2075240712544864</v>
+        <v>0.2078126011396446</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9571,7 +9571,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.406491119240863</v>
+        <v>0.4023432506771807</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9579,22 +9579,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2637076000493286</v>
+        <v>0.2656076000493286</v>
       </c>
       <c r="C100">
-        <v>-1150.642541375811</v>
+        <v>-1172.52352850621</v>
       </c>
       <c r="D100">
-        <v>520.595458624189</v>
+        <v>516.0954714937897</v>
       </c>
       <c r="E100">
-        <v>1662.138</v>
+        <v>1679.519</v>
       </c>
       <c r="F100">
-        <v>1703.338</v>
+        <v>1720.719</v>
       </c>
       <c r="G100">
         <v>32.1</v>
@@ -9615,37 +9615,37 @@
         <v>161.6</v>
       </c>
       <c r="M100">
-        <v>401.6471004000001</v>
+        <v>405.7455402000001</v>
       </c>
       <c r="N100">
-        <v>-240.0471004000001</v>
+        <v>-244.1455402000001</v>
       </c>
       <c r="O100">
-        <v>-70.81389461800002</v>
+        <v>-72.02293435900002</v>
       </c>
       <c r="P100">
-        <v>-169.233205782</v>
+        <v>-172.1226058410001</v>
       </c>
       <c r="Q100">
-        <v>-77.03320578200001</v>
+        <v>-79.92260584100003</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.002562546623839</v>
+        <v>5.959325093247678</v>
       </c>
       <c r="T100">
-        <v>45.74017623309737</v>
+        <v>91.48035246619473</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.1186912589497683</v>
+        <v>0.1174923573442151</v>
       </c>
       <c r="W100">
-        <v>0.2078126011396446</v>
+        <v>0.2080953021382341</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9653,91 +9653,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.4023432506771807</v>
+        <v>0.3982791774380173</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2656076000493286</v>
-      </c>
-      <c r="C101">
-        <v>-1172.52352850621</v>
-      </c>
-      <c r="D101">
-        <v>516.0954714937897</v>
-      </c>
-      <c r="E101">
-        <v>1679.519</v>
-      </c>
-      <c r="F101">
-        <v>1720.719</v>
-      </c>
-      <c r="G101">
-        <v>32.1</v>
-      </c>
-      <c r="H101">
-        <v>1696.9</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>253.8</v>
-      </c>
-      <c r="K101">
-        <v>92.20000000000002</v>
-      </c>
-      <c r="L101">
-        <v>161.6</v>
-      </c>
-      <c r="M101">
-        <v>405.7455402000001</v>
-      </c>
-      <c r="N101">
-        <v>-244.1455402000001</v>
-      </c>
-      <c r="O101">
-        <v>-72.02293435900002</v>
-      </c>
-      <c r="P101">
-        <v>-172.1226058410001</v>
-      </c>
-      <c r="Q101">
-        <v>-79.92260584100003</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.959325093247678</v>
-      </c>
-      <c r="T101">
-        <v>91.48035246619473</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.1174923573442151</v>
-      </c>
-      <c r="W101">
-        <v>0.2080953021382341</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3982791774380173</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
